--- a/DOSSIES_MULTIFORMATO/SEAS/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/SEAS/dossie.xlsx
@@ -752,12 +752,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2016NE00705</t>
+          <t>2016NE00704</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3/2014</t>
+          <t>3/2016</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9997.25</v>
+        <v>1500</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -775,14 +775,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2º Termo Aditivo ao Termo de Contrato 03/2014 Objeto: Reequilibrio econômico-financeiro de 10,96% mais prorrogação de prazo Vigência:12 (doze) meses Valor Global: R$ 119.967,00 Valor Mensal: R$ 9.997,</t>
+          <t>Termo de Contrato n. 003/2016-SEAS Objeto: Contratação, por dispensa de licitação, de pessoa jurídica especializada em Licença de uso de Sistema de Informação, para atender as necessidades da Secretar</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2016NE00712</t>
+          <t>2016NE00707</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -812,12 +812,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2016NE00706</t>
+          <t>2016NE00714</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>3/2014</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>454.46</v>
+        <v>9997.25</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -835,14 +835,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Termo de Contrato nº 02/2016 Objeto: Contratação, por dispensa de licitação, compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem para armazenamento de dados. Val</t>
+          <t>2º Termo Aditivo ao Termo de Contrato 03/2014 Objeto: Reequilibrio econômico-financeiro de 10,96% mais prorrogação de prazo Vigência:12 (doze) meses Valor Global: R$ 119.967,00 Valor Mensal: R$ 9.997,</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2016NE00713</t>
+          <t>2016NE00711</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9997.25</v>
+        <v>3984</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -861,14 +861,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Anulação da NE 0705/2016, em virtude de descrição incorreta</t>
+          <t>Anulação da NE 0707/2016, em virtude do valor na descrição estar incorreto</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2016NE00711</t>
+          <t>2016NE00713</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3984</v>
+        <v>9997.25</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -887,19 +887,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anulação da NE 0707/2016, em virtude do valor na descrição estar incorreto</t>
+          <t>Anulação da NE 0705/2016, em virtude de descrição incorreta</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2016NE00714</t>
+          <t>2016NE00706</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3/2014</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9997.25</v>
+        <v>454.46</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -917,14 +917,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2º Termo Aditivo ao Termo de Contrato 03/2014 Objeto: Reequilibrio econômico-financeiro de 10,96% mais prorrogação de prazo Vigência:12 (doze) meses Valor Global: R$ 119.967,00 Valor Mensal: R$ 9.997,</t>
+          <t>Termo de Contrato nº 02/2016 Objeto: Contratação, por dispensa de licitação, compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem para armazenamento de dados. Val</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2016NE00707</t>
+          <t>2016NE00712</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -954,12 +954,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2016NE00704</t>
+          <t>2016NE00705</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3/2016</t>
+          <t>3/2014</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1500</v>
+        <v>9997.25</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Termo de Contrato n. 003/2016-SEAS Objeto: Contratação, por dispensa de licitação, de pessoa jurídica especializada em Licença de uso de Sistema de Informação, para atender as necessidades da Secretar</t>
+          <t>2º Termo Aditivo ao Termo de Contrato 03/2014 Objeto: Reequilibrio econômico-financeiro de 10,96% mais prorrogação de prazo Vigência:12 (doze) meses Valor Global: R$ 119.967,00 Valor Mensal: R$ 9.997,</t>
         </is>
       </c>
     </row>
@@ -1134,10 +1134,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2022NE0000043</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>2022NE0000044</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1/2021</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>31/01/2022</t>
@@ -1153,21 +1157,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anulação que se faz a NE 000041/2022, por erro de digitação na data.</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS, pelo período de 12 meses.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2022NE0000044</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1/2021</t>
-        </is>
-      </c>
+          <t>2022NE0000043</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>31/01/2022</t>
@@ -1183,19 +1183,19 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS, pelo período de 12 meses.</t>
+          <t>Anulação que se faz a NE 000041/2022, por erro de digitação na data.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023NE0000855</t>
+          <t>2023NE0000858</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5/2019</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>964.49</v>
+        <v>143806.62</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
+          <t>Contrato de prestação de serviços de processamento de dados para a geração de relação de benefícios e gestão das entregas do cartão emergencial a famílias com vulnerabilidade social. TC: 0012/2021 AD:</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2023NE0000858</t>
+          <t>2023NE0000855</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>5/2019</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>143806.62</v>
+        <v>964.49</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Contrato de prestação de serviços de processamento de dados para a geração de relação de benefícios e gestão das entregas do cartão emergencial a famílias com vulnerabilidade social. TC: 0012/2021 AD:</t>
+          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2019NE00292</t>
+          <t>2019NE00293</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1213.91</v>
+        <v>1741.95</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1325,14 +1325,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Anulação de Saldo remanescente 3º Termo Aditivo ao Contrato nº 003/2016 - SEAS. Objeto: Serviços de Licenciamento de Softwares, Licença de Uso de Sistema de Protocolo em Plataforma Web. Trimestre (abr</t>
+          <t xml:space="preserve">Anulação saldo remanescente do CT 03/16 - 3º TA - trimestre janeiro a março 2019- 3º Termo Aditivo ao Contrato nº 003/2016-SEAS. Objeto: Contratação de Empresa Especializada na Prestação dos Serviços </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2019NE00293</t>
+          <t>2019NE00292</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1741.95</v>
+        <v>1213.91</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1351,14 +1351,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anulação saldo remanescente do CT 03/16 - 3º TA - trimestre janeiro a março 2019- 3º Termo Aditivo ao Contrato nº 003/2016-SEAS. Objeto: Contratação de Empresa Especializada na Prestação dos Serviços </t>
+          <t>Anulação de Saldo remanescente 3º Termo Aditivo ao Contrato nº 003/2016 - SEAS. Objeto: Serviços de Licenciamento de Softwares, Licença de Uso de Sistema de Protocolo em Plataforma Web. Trimestre (abr</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2016NE00550</t>
+          <t>2016NE00552</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1381,19 +1381,19 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0130/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
+          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0132/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2016NE00553</t>
+          <t>2016NE00549</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3/2014</t>
+          <t>49/2010</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>9009.780000000001</v>
+        <v>1978.43</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1411,14 +1411,14 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0134/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
+          <t>Reconhecimento da Divida - RD nº 0041/2016: Termo de Contrato n. 049/2010-SEAS-Contratação de Empresa para Prestação de Serviços de Informática, conforme NFS-e nº 15479, emitida em 29/08/2015. Fundame</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2016NE00551</t>
+          <t>2016NE00554</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0131/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
+          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0129/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2016NE00554</t>
+          <t>2016NE00551</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1471,19 +1471,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0129/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
+          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0131/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2016NE00549</t>
+          <t>2016NE00553</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>49/2010</t>
+          <t>3/2014</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1978.43</v>
+        <v>9009.780000000001</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1501,14 +1501,14 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Reconhecimento da Divida - RD nº 0041/2016: Termo de Contrato n. 049/2010-SEAS-Contratação de Empresa para Prestação de Serviços de Informática, conforme NFS-e nº 15479, emitida em 29/08/2015. Fundame</t>
+          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0134/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2016NE00552</t>
+          <t>2016NE00550</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0132/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
+          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0130/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
         </is>
       </c>
     </row>
@@ -1568,7 +1568,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2015NE00083</t>
+          <t>2015NE00082</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1591,14 +1591,14 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Termo de Contrato nº 03/2014</t>
+          <t>Anulação que se faz a n.e 49, por erro de digitação no subgrupo da natureza de despesa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2015NE00082</t>
+          <t>2015NE00083</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Anulação que se faz a n.e 49, por erro de digitação no subgrupo da natureza de despesa</t>
+          <t>Termo de Contrato nº 03/2014</t>
         </is>
       </c>
     </row>
@@ -1688,21 +1688,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2020NE00309</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>16/2017</t>
-        </is>
-      </c>
+          <t>2020NE00305</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>29/09/2020</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>33126.98</v>
+        <v>7550.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1711,24 +1707,28 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CT nº 16/2017 - Objeto: Prestação de serviços de Desenvolvimento de Sistema de Informação. conforme Parecer Jurídico nº 218/2020-ASSESSORIA JURÍDICA, despesa referente ao mês de junho/2018.</t>
+          <t>Anulação que se faz a N.E 00298, por incorreção no subgrupo da natureza de despesa.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2020NE00306</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>2020NE00310</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>16/2017</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
           <t>29/09/2020</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>7550.1</v>
+        <v>33126.98</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1737,14 +1737,14 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Atender despesa com reconhecimento de divida RD Nº 05/2020 - referente ao mês de junho/2019- prestação de serviços de sistema Acesso Gerenciamento à rede mundial..</t>
+          <t>CT.16/2017-Objeto: Prestação de serviços de Desenvolvimento de Sistema de Informação. conforme Parecer Jurídico nº 220/2020-ASSESSORIA JURÍDICA, despesa referente ao mês de julho/2018.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2020NE00308</t>
+          <t>2020NE00304</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1763,14 +1763,14 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atender despesa com reconhecimento de divida RD Nº 06/2020 - referente ao mês de julho/2019- prestação de serviços de sistema Acesso Gerenciamento da Rede.</t>
+          <t>Anulação que se faz a N.E 00297, por incorreção no subgrupo da natureza de despesa.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2020NE00304</t>
+          <t>2020NE00308</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1789,28 +1789,24 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Anulação que se faz a N.E 00297, por incorreção no subgrupo da natureza de despesa.</t>
+          <t>Atender despesa com reconhecimento de divida RD Nº 06/2020 - referente ao mês de julho/2019- prestação de serviços de sistema Acesso Gerenciamento da Rede.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2020NE00310</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>16/2017</t>
-        </is>
-      </c>
+          <t>2020NE00306</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>29/09/2020</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>33126.98</v>
+        <v>7550.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1819,24 +1815,28 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CT.16/2017-Objeto: Prestação de serviços de Desenvolvimento de Sistema de Informação. conforme Parecer Jurídico nº 220/2020-ASSESSORIA JURÍDICA, despesa referente ao mês de julho/2018.</t>
+          <t>Atender despesa com reconhecimento de divida RD Nº 05/2020 - referente ao mês de junho/2019- prestação de serviços de sistema Acesso Gerenciamento à rede mundial..</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2020NE00305</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>2020NE00309</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>16/2017</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
           <t>29/09/2020</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>7550.1</v>
+        <v>33126.98</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1845,21 +1845,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Anulação que se faz a N.E 00298, por incorreção no subgrupo da natureza de despesa.</t>
+          <t>CT nº 16/2017 - Objeto: Prestação de serviços de Desenvolvimento de Sistema de Informação. conforme Parecer Jurídico nº 218/2020-ASSESSORIA JURÍDICA, despesa referente ao mês de junho/2018.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2016NE00670</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2/2016</t>
-        </is>
-      </c>
+          <t>2016NE00671</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>29/09/2016</t>
@@ -1875,17 +1871,21 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Termo de Contrato nº 02/2016 - referente aos meses de julho, agosto e setembro/2016 Objeto: Contratação, por dispensa de licitação, compreendendo o desenvolvimento de Website de transparência a esta S</t>
+          <t>Anulação que se faz a n.e. 670, por erro de digitação no valor a ser empenhado</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2016NE00671</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>2016NE00672</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2/2016</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
           <t>29/09/2016</t>
@@ -1901,19 +1901,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Anulação que se faz a n.e. 670, por erro de digitação no valor a ser empenhado</t>
+          <t>Termo de Contrato nº 02/2016 Objeto: Contratação, por dispensa de licitação, compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem para armazenamento de dados.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2016NE00670</t>
+          <t>2016NE00673</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>3/2014</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1363.38</v>
+        <v>29991.75</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Termo de Contrato nº 02/2016 - referente aos meses de julho, agosto e setembro/2016 Objeto: Contratação, por dispensa de licitação, compreendendo o desenvolvimento de Website de transparência a esta S</t>
+          <t>2 Aditivo ao Termo de Contrato n 03-2014</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1968,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2016NE00673</t>
+          <t>2016NE00670</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>3/2014</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>29991.75</v>
+        <v>1363.38</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1991,21 +1991,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2 Aditivo ao Termo de Contrato n 03-2014</t>
+          <t>Termo de Contrato nº 02/2016 - referente aos meses de julho, agosto e setembro/2016 Objeto: Contratação, por dispensa de licitação, compreendendo o desenvolvimento de Website de transparência a esta S</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2016NE00672</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2/2016</t>
-        </is>
-      </c>
+          <t>2016NE00671</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
           <t>29/09/2016</t>
@@ -2021,17 +2017,21 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Termo de Contrato nº 02/2016 Objeto: Contratação, por dispensa de licitação, compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem para armazenamento de dados.</t>
+          <t>Anulação que se faz a n.e. 670, por erro de digitação no valor a ser empenhado</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2016NE00671</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>2016NE00670</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2/2016</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
           <t>29/09/2016</t>
@@ -2047,21 +2047,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anulação que se faz a n.e. 670, por erro de digitação no valor a ser empenhado</t>
+          <t>Termo de Contrato nº 02/2016 - referente aos meses de julho, agosto e setembro/2016 Objeto: Contratação, por dispensa de licitação, compreendendo o desenvolvimento de Website de transparência a esta S</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2019NE00260</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>16/2017</t>
-        </is>
-      </c>
+          <t>2019NE00262</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>29/08/2019</t>
@@ -2077,17 +2073,21 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2º Termo Aditivo ao Contrato nº 016/2017 - SEAS. Objeto: Contratação de Empresa Especializada na Prestação dos Serviços de Desenvolvimento e Hospedagem de Sistemas de Informações para Implantação das </t>
+          <t>Anulação da NE nº 260/2019, por erro de descrição.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2019NE00262</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>2019NE00260</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>16/2017</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr">
         <is>
           <t>29/08/2019</t>
@@ -2103,14 +2103,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anulação da NE nº 260/2019, por erro de descrição.</t>
+          <t xml:space="preserve">2º Termo Aditivo ao Contrato nº 016/2017 - SEAS. Objeto: Contratação de Empresa Especializada na Prestação dos Serviços de Desenvolvimento e Hospedagem de Sistemas de Informações para Implantação das </t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2022NE0000248</t>
+          <t>2022NE0000249</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>819.42</v>
+        <v>822.46</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Execução de sistemas SISTEMA: Sist. de Recursos Humanos e Folha Faturamento mínimo por folha - até 200 funcionários processados, conforme PARECER Nº 331/2021 – ASSEJUR/SEAS</t>
+          <t>Execução de sistemas SISTEMA: Sist. de Recursos Humanos e Folha Faturamento mínimo por folha - até 200 funcionários processados, conforme PARECER Nº 357/2021 – ASSEJUR/SEAS</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2022NE0000249</t>
+          <t>2022NE0000248</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>822.46</v>
+        <v>819.42</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Execução de sistemas SISTEMA: Sist. de Recursos Humanos e Folha Faturamento mínimo por folha - até 200 funcionários processados, conforme PARECER Nº 357/2021 – ASSEJUR/SEAS</t>
+          <t>Execução de sistemas SISTEMA: Sist. de Recursos Humanos e Folha Faturamento mínimo por folha - até 200 funcionários processados, conforme PARECER Nº 331/2021 – ASSEJUR/SEAS</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2018NE00438</t>
+          <t>2018NE00439</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>8851.08</v>
+        <v>92034.88</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2018NE00440</t>
+          <t>2018NE00437</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>91308.92</v>
+        <v>48.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2018NE00437</t>
+          <t>2018NE00440</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>48.4</v>
+        <v>91308.92</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2018NE00439</t>
+          <t>2018NE00438</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>92034.88</v>
+        <v>8851.08</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2023NE0000850</t>
+          <t>2023NE0000852</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>909.29</v>
+        <v>150000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ANULAÇÃO Saldo remanescente do 1º Termo Aditivo ao Contrato nº 007/2021-SEAS, para ajuste orçamentário e encerramento do Termo de Contrato.</t>
+          <t>ANULAÇÃO Saldo remanescente do 1º Termo Aditivo ao Contrato nº 012/2021-SEAS, para ajuste orçamentário e encerramento do exercício 2023.</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2023NE0000852</t>
+          <t>2023NE0000850</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>150000</v>
+        <v>909.29</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ANULAÇÃO Saldo remanescente do 1º Termo Aditivo ao Contrato nº 012/2021-SEAS, para ajuste orçamentário e encerramento do exercício 2023.</t>
+          <t>ANULAÇÃO Saldo remanescente do 1º Termo Aditivo ao Contrato nº 007/2021-SEAS, para ajuste orçamentário e encerramento do Termo de Contrato.</t>
         </is>
       </c>
     </row>
@@ -2486,12 +2486,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2022NE0000237</t>
+          <t>2022NE0000240</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5/2019</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>39584.47</v>
+        <v>148331.11</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2509,19 +2509,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>REFORÇO 2022NE000023 - SALDO 2º TAC nº 05/2019 - PRODAM</t>
+          <t>REFORÇO 2022NE0000026 - SALDO CT nº 012/2021</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2022NE0000238</t>
+          <t>2022NE0000239</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>4671.36</v>
+        <v>6358.06</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2539,19 +2539,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>REFORÇO 2022NE0000044 - SALDO 1º TAC 01/2021</t>
+          <t>REFORÇO 2022NE000024 - SALDO CT nº 007/2021</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2022NE0000239</t>
+          <t>2022NE0000238</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>6358.06</v>
+        <v>4671.36</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2569,19 +2569,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>REFORÇO 2022NE000024 - SALDO CT nº 007/2021</t>
+          <t>REFORÇO 2022NE0000044 - SALDO 1º TAC 01/2021</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2022NE0000240</t>
+          <t>2022NE0000237</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>5/2019</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>148331.11</v>
+        <v>39584.47</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>REFORÇO 2022NE0000026 - SALDO CT nº 012/2021</t>
+          <t>REFORÇO 2022NE000023 - SALDO 2º TAC nº 05/2019 - PRODAM</t>
         </is>
       </c>
     </row>
@@ -2636,10 +2636,14 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2017NE00267</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
+          <t>2017NE00261</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>3/2014</t>
+        </is>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
           <t>28/04/2017</t>
@@ -2655,14 +2659,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE 261/2017 POR ERRO DE DESCRIÇÃO.</t>
+          <t>SERVIÇOS DE LINK DE COMUNICAÇÃO PARA ATENDER AS NECESSIDADES DA SEAS.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2017NE00264</t>
+          <t>2017NE00260</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2672,7 +2676,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4425.87</v>
+        <v>32848.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2681,19 +2685,19 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE 257/2017 POR ERRO DE DESCRIÇÃO.</t>
+          <t>ANULAÇÃO DA NE 259/2017, POR ERRO DE DIGITAÇÃO NO VALOR GLOBAL.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2017NE00265</t>
+          <t>2017NE00268</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>3/2014</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2702,7 +2706,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>4425.87</v>
+        <v>32848.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2711,7 +2715,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMATICA, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTICIAS, VIDEOS E IMAGENS WEBSITE.</t>
+          <t>SERVIÇOS DE LINK DE COMUNICAÇÃO PARA ATENDER AS NECESSIDADES DA SEAS.</t>
         </is>
       </c>
     </row>
@@ -2748,12 +2752,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2017NE00268</t>
+          <t>2017NE00265</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3/2014</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2762,7 +2766,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>32848.2</v>
+        <v>4425.87</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2771,14 +2775,14 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LINK DE COMUNICAÇÃO PARA ATENDER AS NECESSIDADES DA SEAS.</t>
+          <t>SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMATICA, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTICIAS, VIDEOS E IMAGENS WEBSITE.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2017NE00260</t>
+          <t>2017NE00264</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -2788,7 +2792,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>32848.2</v>
+        <v>4425.87</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2797,21 +2801,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE 259/2017, POR ERRO DE DIGITAÇÃO NO VALOR GLOBAL.</t>
+          <t>ANULAÇÃO DA NE 257/2017 POR ERRO DE DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2017NE00261</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>3/2014</t>
-        </is>
-      </c>
+          <t>2017NE00267</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
           <t>28/04/2017</t>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LINK DE COMUNICAÇÃO PARA ATENDER AS NECESSIDADES DA SEAS.</t>
+          <t>ANULAÇÃO DA NE 261/2017 POR ERRO DE DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2024NE0000608</t>
+          <t>2024NE0000607</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>9966.120000000001</v>
+        <v>906.29</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Anulação do saldo remanescente da 2024NE000263, Contrato/Ajustes Nº 0003/2021 Aditivo Nº 03 - Objeto: Contratação de empresa especializada na prestação de serviços de manutenção de PROXY, serviço de s</t>
+          <t>Anulação do saldo remanescente da 2024NE000008, referente ao Contrato Nº 0007/2021 Aditivo Nº 02, Objeto: Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gesto</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2024NE0000607</t>
+          <t>2024NE0000608</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>906.29</v>
+        <v>9966.120000000001</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -2961,19 +2961,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Anulação do saldo remanescente da 2024NE000008, referente ao Contrato Nº 0007/2021 Aditivo Nº 02, Objeto: Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gesto</t>
+          <t>Anulação do saldo remanescente da 2024NE000263, Contrato/Ajustes Nº 0003/2021 Aditivo Nº 03 - Objeto: Contratação de empresa especializada na prestação de serviços de manutenção de PROXY, serviço de s</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2023NE0000693</t>
+          <t>2023NE0000699</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>5/2019</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1189.06</v>
+        <v>13503</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -2991,19 +2991,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para a publicação de informações, noticias, vídeos e imagens website. TC: 0007/2021 AD: </t>
+          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2023NE0000699</t>
+          <t>2023NE0000693</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5/2019</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13503</v>
+        <v>1189.06</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3021,28 +3021,24 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
+          <t xml:space="preserve">Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para a publicação de informações, noticias, vídeos e imagens website. TC: 0007/2021 AD: </t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2017NE00257</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>10/2016</t>
-        </is>
-      </c>
+          <t>2017NE00258</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
           <t>27/04/2017</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>4425.87</v>
+        <v>32848.2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3051,7 +3047,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMATICA, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTICIAS, VIDEOS E IMAGENS WEBSITE.</t>
+          <t>ANULAÇÃO DA NE 256/2017 POR ERRO DE DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
@@ -3088,17 +3084,21 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2017NE00258</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>2017NE00257</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>10/2016</t>
+        </is>
+      </c>
       <c r="C88" t="inlineStr">
         <is>
           <t>27/04/2017</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>32848.2</v>
+        <v>4425.87</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE 256/2017 POR ERRO DE DESCRIÇÃO.</t>
+          <t>SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMATICA, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTICIAS, VIDEOS E IMAGENS WEBSITE.</t>
         </is>
       </c>
     </row>
@@ -3237,11 +3237,7 @@
           <t>2022NE0000222</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>3/2021</t>
-        </is>
-      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
           <t>26/04/2022</t>
@@ -3267,7 +3263,11 @@
           <t>2022NE0000222</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>3/2021</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
           <t>26/04/2022</t>
@@ -3346,7 +3346,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2020NE00296</t>
+          <t>2020NE00298</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2435.51</v>
+        <v>7550.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Atender despesa com reconhecimento de divida RD Nº 07/2020 - referente ao mês de maio/2019- prestação de serviços de sistema Acesso Gerenciamento da Rede.</t>
+          <t>Atender despesa com reconhecimento de divida RD Nº 06/2020 - referente ao mês de julho/2019- prestação de serviços de sistema Acesso Gerenciamento da Rede.</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2020NE00298</t>
+          <t>2020NE00296</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>7550.1</v>
+        <v>2435.51</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Atender despesa com reconhecimento de divida RD Nº 06/2020 - referente ao mês de julho/2019- prestação de serviços de sistema Acesso Gerenciamento da Rede.</t>
+          <t>Atender despesa com reconhecimento de divida RD Nº 07/2020 - referente ao mês de maio/2019- prestação de serviços de sistema Acesso Gerenciamento da Rede.</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2017NE00291</t>
+          <t>2017NE00292</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>3998.63</v>
+        <v>3771.78</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3537,14 +3537,14 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Atender despesa para pagamento de Reconhecimento de Dívida, referente mês de novembro/2014 do Cont. 49/2010</t>
+          <t>Atender despesa para pagamento de Reconhecimento de Dívida, referente mês de dezembro/2014 do Cont. 49/2010</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2017NE00292</t>
+          <t>2017NE00291</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>3771.78</v>
+        <v>3998.63</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Atender despesa para pagamento de Reconhecimento de Dívida, referente mês de dezembro/2014 do Cont. 49/2010</t>
+          <t>Atender despesa para pagamento de Reconhecimento de Dívida, referente mês de novembro/2014 do Cont. 49/2010</t>
         </is>
       </c>
     </row>
@@ -3634,10 +3634,14 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2020NE00207</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
+          <t>2020NE00206</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>11/2014</t>
+        </is>
+      </c>
       <c r="C107" t="inlineStr">
         <is>
           <t>23/07/2020</t>
@@ -3653,21 +3657,17 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Anulação que se faz a n.e 206, por erro de digitação no numero do processo.</t>
+          <t>Reconhecimento de Dívida Nº 235 do Contrato nº 011/2014, prestação de serviço de sistema SPROWEB Protocolo, mes de setembro/2015, Nota Fiscal nº 16103, emitida em 02/10/2015.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2020NE00206</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>11/2014</t>
-        </is>
-      </c>
+          <t>2020NE00207</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
           <t>23/07/2020</t>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Reconhecimento de Dívida Nº 235 do Contrato nº 011/2014, prestação de serviço de sistema SPROWEB Protocolo, mes de setembro/2015, Nota Fiscal nº 16103, emitida em 02/10/2015.</t>
+          <t>Anulação que se faz a n.e 206, por erro de digitação no numero do processo.</t>
         </is>
       </c>
     </row>
@@ -3720,12 +3720,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2021NE0000294</t>
+          <t>2021NE0000295</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>55424.25</v>
+        <v>8843.719999999999</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3743,19 +3743,19 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE Nº 023/2021 - Contrato nº 12/2020-SEAS, tendo como objeto: Contratação de Empresa Especializada na Prestação dos Serviços de Processamento de dados para geração das informações do cartão</t>
+          <t>REFORÇO DA NE Nº 031/2021 - Termo de Contrato nº 001/2021-SEAS. Objeto do Contrato: Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWEB, p</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2021NE0000295</t>
+          <t>2021NE0000294</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3764,7 +3764,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>8843.719999999999</v>
+        <v>55424.25</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE Nº 031/2021 - Termo de Contrato nº 001/2021-SEAS. Objeto do Contrato: Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWEB, p</t>
+          <t>REFORÇO DA NE Nº 023/2021 - Contrato nº 12/2020-SEAS, tendo como objeto: Contratação de Empresa Especializada na Prestação dos Serviços de Processamento de dados para geração das informações do cartão</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2025NE0000599</t>
+          <t>2025NE0000598</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5/2024</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>29152.63</v>
+        <v>143675.44</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3833,19 +3833,19 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Contratação de empresa prestadora de serviços de tecnologia da informação, para atender as necessidades desta SEAS.</t>
+          <t>Contrato de prestação de serviços de processamento de dados para a geração de relação de benefícios e gestão das entregas do cartão emergencial a famílias com vulnerabilidade social. TC: 0012/2021 AD:</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025NE0000598</t>
+          <t>2025NE0000599</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>5/2024</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>143675.44</v>
+        <v>29152.63</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Contrato de prestação de serviços de processamento de dados para a geração de relação de benefícios e gestão das entregas do cartão emergencial a famílias com vulnerabilidade social. TC: 0012/2021 AD:</t>
+          <t>Contratação de empresa prestadora de serviços de tecnologia da informação, para atender as necessidades desta SEAS.</t>
         </is>
       </c>
     </row>
@@ -4004,12 +4004,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2020NE00145</t>
+          <t>2020NE00151</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5/2019</t>
+          <t>16/2017</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>26517.6</v>
+        <v>112986.94</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4027,19 +4027,19 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Termo de Contrato nº 005/2019-SEAS. Objeto do Contrato: Contratação de Pessoa Jurídica Especializada no Serviços de Acesso a Internet por Fibra Ótica com com garantia de 100% em download e upload, par</t>
+          <t>2º Termo Aditivo ao Contrato nº 016/2017 - SEAS. Objeto do Contrato: Serviço de Desenvolvimento e Hospedagem de Sistemas de Informações para Implantação das Plataformas Eletrônicas sobre o Cofinanciam</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2020NE00141</t>
+          <t>2020NE00149</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>3/2016</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>12379.15</v>
+        <v>3025.04</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4057,19 +4057,19 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4º Termo Aditivo ao Contrato nº 003/2016 -SEAS. Objeto: Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWEB, para atender as necessidades </t>
+          <t xml:space="preserve">3º Termo Aditivo ao Contrato nº 010/2016-SEAS. Objeto do Contrato: Serviços de Licença de Uso de Sistema de Informática, Compreendendo a Disponibilização de Gestor de Conteúdo Web, para Publicação de </t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2020NE00149</t>
+          <t>2020NE00141</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>3/2016</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>3025.04</v>
+        <v>12379.15</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4087,19 +4087,19 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3º Termo Aditivo ao Contrato nº 010/2016-SEAS. Objeto do Contrato: Serviços de Licença de Uso de Sistema de Informática, Compreendendo a Disponibilização de Gestor de Conteúdo Web, para Publicação de </t>
+          <t xml:space="preserve">4º Termo Aditivo ao Contrato nº 003/2016 -SEAS. Objeto: Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWEB, para atender as necessidades </t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2020NE00151</t>
+          <t>2020NE00145</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>16/2017</t>
+          <t>5/2019</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>112986.94</v>
+        <v>26517.6</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2º Termo Aditivo ao Contrato nº 016/2017 - SEAS. Objeto do Contrato: Serviço de Desenvolvimento e Hospedagem de Sistemas de Informações para Implantação das Plataformas Eletrônicas sobre o Cofinanciam</t>
+          <t>Termo de Contrato nº 005/2019-SEAS. Objeto do Contrato: Contratação de Pessoa Jurídica Especializada no Serviços de Acesso a Internet por Fibra Ótica com com garantia de 100% em download e upload, par</t>
         </is>
       </c>
     </row>
@@ -4184,12 +4184,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2021NE0000026</t>
+          <t>2021NE0000017</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3/2016</t>
+          <t>16/2017</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1026.85</v>
+        <v>36447.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4207,19 +4207,19 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Reforço a 202100014, 4º Termo Aditivo ao Contrato nº 003/2016-SEAS. Objeto do Contrato: Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWE</t>
+          <t>3º Termo Aditivo ao Contrato nº 016/2017 - SEAS. Objeto do Contrato: Serviço de Desenvolvimento e Hospedagem de Sistemas de Informações para Implantação das Plataformas Eletrônicas sobre o Cofinanciam</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2021NE0000020</t>
+          <t>2021NE0000023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5/2019</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>53035.2</v>
+        <v>221697</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4237,19 +4237,19 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Prestação de Serviços de Acesso à Internet por Fibra Ótica com garantia de 100% em download e upload para atender as necessidades da SEAS e suas Unidades.</t>
+          <t>Prestação de Serviços de de Processamento de Dados para geração das informações do cartão de benefícios para concessão de auxilio emergência pelo Governo do Estado do Amazonas.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2021NE0000014</t>
+          <t>2021NE0000016</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3/2016</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>741.6</v>
+        <v>6050.08</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4267,19 +4267,19 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS.</t>
+          <t>Serviço de Licença e Uso de Sistema de Informatica compreendendo a disponibilização de gestor de conteúdo web par publicação de informações, noticias, videos e imagens website.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2021NE0000016</t>
+          <t>2021NE0000014</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>3/2016</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>6050.08</v>
+        <v>741.6</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4297,19 +4297,19 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Serviço de Licença e Uso de Sistema de Informatica compreendendo a disponibilização de gestor de conteúdo web par publicação de informações, noticias, videos e imagens website.</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2021NE0000023</t>
+          <t>2021NE0000020</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>5/2019</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>221697</v>
+        <v>53035.2</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4327,19 +4327,19 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Prestação de Serviços de de Processamento de Dados para geração das informações do cartão de benefícios para concessão de auxilio emergência pelo Governo do Estado do Amazonas.</t>
+          <t>Prestação de Serviços de Acesso à Internet por Fibra Ótica com garantia de 100% em download e upload para atender as necessidades da SEAS e suas Unidades.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2021NE0000017</t>
+          <t>2021NE0000026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>16/2017</t>
+          <t>3/2016</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>36447.4</v>
+        <v>1026.85</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4357,14 +4357,14 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>3º Termo Aditivo ao Contrato nº 016/2017 - SEAS. Objeto do Contrato: Serviço de Desenvolvimento e Hospedagem de Sistemas de Informações para Implantação das Plataformas Eletrônicas sobre o Cofinanciam</t>
+          <t>Reforço a 202100014, 4º Termo Aditivo ao Contrato nº 003/2016-SEAS. Objeto do Contrato: Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWE</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2015NE00706</t>
+          <t>2015NE00707</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>8701.379999999999</v>
+        <v>27029.34</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4387,14 +4387,14 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Termo de Contrato nº 03/2014 - mes de abril/2015 Objeto: Prestação de serviços de técnicos em telecomunicações com banda de 3 Mbps Valor do Contrato: R$ 104.416,56 Valor Mensal: R$ 8.701,38 Vigência: </t>
+          <t>Cobertura de junho/julho e agosto/2015</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2015NE00707</t>
+          <t>2015NE00706</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>27029.34</v>
+        <v>8701.379999999999</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4417,14 +4417,14 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Cobertura de junho/julho e agosto/2015</t>
+          <t xml:space="preserve">Termo de Contrato nº 03/2014 - mes de abril/2015 Objeto: Prestação de serviços de técnicos em telecomunicações com banda de 3 Mbps Valor do Contrato: R$ 104.416,56 Valor Mensal: R$ 8.701,38 Vigência: </t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2020NE00199</t>
+          <t>2020NE00198</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4447,14 +4447,14 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Reconhecimento de Dívida Nº 234 do Contrato nº 011/2014, prestação de serviço de sistema SPROWEB Protocolo, mes de agosto/2015, Nota Fiscal nº 16102</t>
+          <t>Reconhecimento de Dívida Nº 237 do Contrato nº 011/2014, prestação de serviço de sistema SPROWEB Protocolo, mes de novembro a 2015, Nota Fiscal nº 16782</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2020NE00197</t>
+          <t>2020NE00196</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4477,14 +4477,14 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Reconhecimento de Dívida Nº 235 do Contrato nº 011/2014, prestação de serviço de sistema SPROWEB Protocolo, mes de setembro/2015, Nota Fiscal nº 16103</t>
+          <t>Reconhecimento de Dívida Nº 233 do Contrato nº 011/2014, prestação de serviço de sistema SPROWEB Protocolo, mes de julho a 2015, Nota Fiscal nº 16101</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2020NE00196</t>
+          <t>2020NE00197</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4507,14 +4507,14 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Reconhecimento de Dívida Nº 233 do Contrato nº 011/2014, prestação de serviço de sistema SPROWEB Protocolo, mes de julho a 2015, Nota Fiscal nº 16101</t>
+          <t>Reconhecimento de Dívida Nº 235 do Contrato nº 011/2014, prestação de serviço de sistema SPROWEB Protocolo, mes de setembro/2015, Nota Fiscal nº 16103</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2020NE00198</t>
+          <t>2020NE00199</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Reconhecimento de Dívida Nº 237 do Contrato nº 011/2014, prestação de serviço de sistema SPROWEB Protocolo, mes de novembro a 2015, Nota Fiscal nº 16782</t>
+          <t>Reconhecimento de Dívida Nº 234 do Contrato nº 011/2014, prestação de serviço de sistema SPROWEB Protocolo, mes de agosto/2015, Nota Fiscal nº 16102</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2022NE0000713</t>
+          <t>2022NE0000712</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>42031.2</v>
+        <v>66273.92</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4589,14 +4589,14 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Anulação Saldo remanescente do Contrato: 03/2021 - Processo: 760/2020 - Vigência: 03/05/2021 ate 03/05/2022, para ajuste orçamentário. 42.031,20</t>
+          <t>Anulação Saldo remanescente do Contrato: 16/2017 - Processo: 903/2021 - Vigência: 05.09.21 ate 04.09.22, para ajuste orçamentário.66.273,92</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2022NE0000712</t>
+          <t>2022NE0000713</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>66273.92</v>
+        <v>42031.2</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Anulação Saldo remanescente do Contrato: 16/2017 - Processo: 903/2021 - Vigência: 05.09.21 ate 04.09.22, para ajuste orçamentário.66.273,92</t>
+          <t>Anulação Saldo remanescente do Contrato: 03/2021 - Processo: 760/2020 - Vigência: 03/05/2021 ate 03/05/2022, para ajuste orçamentário. 42.031,20</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4682,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2017NE00658</t>
+          <t>2017NE00657</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>4977</v>
+        <v>1142.2</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4701,14 +4701,14 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE 268/2017, através da INSTRUÇÃO NORMATIVA Nº 001/2017, em virtude de encerramento de exercício.</t>
+          <t>Anulação parcial da NE 218/2017, através da INSTRUÇÃO NORMATIVA Nº 001/2017, em virtude de encerramento de exercício.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2017NE00657</t>
+          <t>2017NE00658</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1142.2</v>
+        <v>4977</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Anulação parcial da NE 218/2017, através da INSTRUÇÃO NORMATIVA Nº 001/2017, em virtude de encerramento de exercício.</t>
+          <t>Anulação parcial da NE 268/2017, através da INSTRUÇÃO NORMATIVA Nº 001/2017, em virtude de encerramento de exercício.</t>
         </is>
       </c>
     </row>
@@ -4764,12 +4764,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2016NE00746</t>
+          <t>2016NE00751</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>454.46</v>
+        <v>2950.58</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4787,19 +4787,19 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Termo de Contrato nº 02/2016 Objeto: Contratação, por dispensa de licitação, compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem para armazenamento de dados. Val</t>
+          <t>Termo de Contrato nº 10/2016 Objeto: Prestação de serviços para licença de uso de sistema de informação, compreendendo a disponibilização de Gestor de conteúdo Web a essa SEAS, para publicações, notic</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2016NE00745</t>
+          <t>2016NE00747</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>3/2016</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>3000</v>
+        <v>5901.16</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -4817,24 +4817,28 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Termo de Contrato nº 003/2016-SEAS Objeto: Contratação, por dispensa de licitação, de pessoa jurídica especializada em Licença de uso de Sistema de Informação, para atender as necessidades da Secretar</t>
+          <t>Termo de Contrato nº 10/2016 Objeto: Prestação de serviços para licença de uso de sistema de informação, compreendendo a disponibilização de Gestor de conteúdo Web a essa SEAS, para publicações, notic</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2016NE00748</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
+          <t>2016NE00744</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1/2016</t>
+        </is>
+      </c>
       <c r="C148" t="inlineStr">
         <is>
           <t>18/11/2016</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>3000</v>
+        <v>3984</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -4843,19 +4847,19 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Anulação da Nota de Empenho n. 0745/2016, em virtude de Descrição da Vigência incorreta</t>
+          <t xml:space="preserve">Termo de Contrato n. 001/2016-SEAS. Objeto: Contratação, por dispensa de licitação, de pessoa jurídica especializada em Serviços Técnicos em Informática, para atender as necessidades desta Secretaria </t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2016NE00749</t>
+          <t>2016NE00743</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3/2016</t>
+          <t>3/2014</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4864,7 +4868,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>3000</v>
+        <v>9997.25</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -4873,7 +4877,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Termo de Contrato nº 003/2016-SEAS Objeto: Contratação, por dispensa de licitação, de pessoa jurídica especializada em Licença de uso de Sistema de Informação, para atender as necessidades da Secretar</t>
+          <t>2º Termo Aditivo ao Termo de Contrato 03/2014 Objeto: Reequilibrio econômico-financeiro de 10,96% mais prorrogação de prazo Valor Global: R$ 119.967,00 Valor Mensal: R$ 9.997,25 Valor Empenhado R$ 9.9</t>
         </is>
       </c>
     </row>
@@ -4906,12 +4910,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2016NE00743</t>
+          <t>2016NE00749</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>3/2014</t>
+          <t>3/2016</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4920,7 +4924,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>9997.25</v>
+        <v>3000</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -4929,28 +4933,24 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2º Termo Aditivo ao Termo de Contrato 03/2014 Objeto: Reequilibrio econômico-financeiro de 10,96% mais prorrogação de prazo Valor Global: R$ 119.967,00 Valor Mensal: R$ 9.997,25 Valor Empenhado R$ 9.9</t>
+          <t>Termo de Contrato nº 003/2016-SEAS Objeto: Contratação, por dispensa de licitação, de pessoa jurídica especializada em Licença de uso de Sistema de Informação, para atender as necessidades da Secretar</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2016NE00744</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>1/2016</t>
-        </is>
-      </c>
+          <t>2016NE00748</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
           <t>18/11/2016</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>3984</v>
+        <v>3000</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -4959,19 +4959,19 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Termo de Contrato n. 001/2016-SEAS. Objeto: Contratação, por dispensa de licitação, de pessoa jurídica especializada em Serviços Técnicos em Informática, para atender as necessidades desta Secretaria </t>
+          <t>Anulação da Nota de Empenho n. 0745/2016, em virtude de Descrição da Vigência incorreta</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2016NE00747</t>
+          <t>2016NE00745</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>3/2016</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>5901.16</v>
+        <v>3000</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -4989,19 +4989,19 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Termo de Contrato nº 10/2016 Objeto: Prestação de serviços para licença de uso de sistema de informação, compreendendo a disponibilização de Gestor de conteúdo Web a essa SEAS, para publicações, notic</t>
+          <t>Termo de Contrato nº 003/2016-SEAS Objeto: Contratação, por dispensa de licitação, de pessoa jurídica especializada em Licença de uso de Sistema de Informação, para atender as necessidades da Secretar</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2016NE00751</t>
+          <t>2016NE00746</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>2950.58</v>
+        <v>454.46</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5019,28 +5019,24 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Termo de Contrato nº 10/2016 Objeto: Prestação de serviços para licença de uso de sistema de informação, compreendendo a disponibilização de Gestor de conteúdo Web a essa SEAS, para publicações, notic</t>
+          <t>Termo de Contrato nº 02/2016 Objeto: Contratação, por dispensa de licitação, compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem para armazenamento de dados. Val</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2025NE0000783</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>12/2021</t>
-        </is>
-      </c>
+          <t>2025NE0000790</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
           <t>18/09/2025</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>25632.2</v>
+        <v>50028.76</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5049,24 +5045,28 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Contrato de prestação de serviços de processamento de dados para a geração de relação de benefícios e gestão das entregas do cartão emergencial a famílias com vulnerabilidade social. TC: 0012/2021 AD:</t>
+          <t>Anulação do saldo remanescente (50.028,76) do TC.05/2024, pela expiração da vigência: 05/08/2024 a 05/08/2025.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2025NE0000790</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr"/>
+          <t>2025NE0000783</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>12/2021</t>
+        </is>
+      </c>
       <c r="C156" t="inlineStr">
         <is>
           <t>18/09/2025</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>50028.76</v>
+        <v>25632.2</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5075,14 +5075,14 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Anulação do saldo remanescente (50.028,76) do TC.05/2024, pela expiração da vigência: 05/08/2024 a 05/08/2025.</t>
+          <t>Contrato de prestação de serviços de processamento de dados para a geração de relação de benefícios e gestão das entregas do cartão emergencial a famílias com vulnerabilidade social. TC: 0012/2021 AD:</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2015NE00758</t>
+          <t>2015NE00759</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
@@ -5101,14 +5101,14 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reconhecimento de Divida. Folha de Informação de Exercícios anteriores nº 0118/2015. Serviços de Licença de uso de sistemas de informação para a disponibilização do Sistema de Protocolo em plataforma </t>
+          <t>Anulação da Nota de Empenho n. 0758/2015, em virtude de valor estar incorreto.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2015NE00760</t>
+          <t>2015NE00757</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>750</v>
+        <v>8701.379999999999</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5127,14 +5127,14 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reconhecimento de Divida. Folha de Informação de Exercícios anteriores nº 0118/2015. Serviços de Licença de uso de sistemas de informação para a disponibilização do Sistema de Protocolo em plataforma </t>
+          <t>Reconhecimento de Divida. Folha de Informação de Exercícios anteriores nº 0120/2015. Serviços de Rede, compreendendo a disponibilidade de acesso a rede de Governo, referente ao mês de novembro/2014, N</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2015NE00757</t>
+          <t>2015NE00760</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>8701.379999999999</v>
+        <v>750</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5153,14 +5153,14 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Reconhecimento de Divida. Folha de Informação de Exercícios anteriores nº 0120/2015. Serviços de Rede, compreendendo a disponibilidade de acesso a rede de Governo, referente ao mês de novembro/2014, N</t>
+          <t xml:space="preserve">Reconhecimento de Divida. Folha de Informação de Exercícios anteriores nº 0118/2015. Serviços de Licença de uso de sistemas de informação para a disponibilização do Sistema de Protocolo em plataforma </t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2015NE00759</t>
+          <t>2015NE00758</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Anulação da Nota de Empenho n. 0758/2015, em virtude de valor estar incorreto.</t>
+          <t xml:space="preserve">Reconhecimento de Divida. Folha de Informação de Exercícios anteriores nº 0118/2015. Serviços de Licença de uso de sistemas de informação para a disponibilização do Sistema de Protocolo em plataforma </t>
         </is>
       </c>
     </row>
@@ -5212,17 +5212,21 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2023NE0000632</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr"/>
+          <t>2023NE0000633</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>5/2019</t>
+        </is>
+      </c>
       <c r="C162" t="inlineStr">
         <is>
           <t>17/07/2023</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>42319</v>
+        <v>14467.49</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5231,19 +5235,19 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Anulação do saldo remanescente do contrato: 03/2021, para ajuste orçamentário.</t>
+          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2023NE0000635</t>
+          <t>2023NE0000637</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>3/2021</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5252,7 +5256,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>215709.93</v>
+        <v>43460.82</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5261,19 +5265,19 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contrato de prestação de serviços de processamento de dados para a geração de relação de benefícios e gestão das entregas do cartão emergencial a famílias com vulnerabilidade social. TC: 012/2021 AD: </t>
+          <t xml:space="preserve">Contratação de empresa especializada na prestação de serviços de manutenção de PROXY, serviço de segurança da informação, serviço de regras de acesso e serviços de FAREWALL em relação a internet. TC: </t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2023NE0000638</t>
+          <t>2023NE0000636</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5282,7 +5286,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>3007.64</v>
+        <v>2462.98</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5291,19 +5295,19 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para a publicação de informações, noticias, vídeos e imagens website. TC: 007/2021 AD: 0</t>
+          <t>Contratação de empresa especializada n prestação dos serviços de licença de uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS, pelo período de 12 Meses. TC: 001/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2023NE0000636</t>
+          <t>2023NE0000638</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5312,7 +5316,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>2462.98</v>
+        <v>3007.64</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5321,19 +5325,19 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada n prestação dos serviços de licença de uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS, pelo período de 12 Meses. TC: 001/2021 AD: 02.</t>
+          <t>Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para a publicação de informações, noticias, vídeos e imagens website. TC: 007/2021 AD: 0</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2023NE0000637</t>
+          <t>2023NE0000635</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>3/2021</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5342,7 +5346,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>43460.82</v>
+        <v>215709.93</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5351,28 +5355,24 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada na prestação de serviços de manutenção de PROXY, serviço de segurança da informação, serviço de regras de acesso e serviços de FAREWALL em relação a internet. TC: </t>
+          <t xml:space="preserve">Contrato de prestação de serviços de processamento de dados para a geração de relação de benefícios e gestão das entregas do cartão emergencial a famílias com vulnerabilidade social. TC: 012/2021 AD: </t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2023NE0000633</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>5/2019</t>
-        </is>
-      </c>
+          <t>2023NE0000632</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr">
         <is>
           <t>17/07/2023</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>14467.49</v>
+        <v>42319</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
+          <t>Anulação do saldo remanescente do contrato: 03/2021, para ajuste orçamentário.</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2021NE0000538</t>
+          <t>2021NE0000536</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>3/2021</t>
+          <t>5/2019</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>36173.2</v>
+        <v>52267.48</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Reforço da 2021NE000316 - Contrato nº 03/2021 ¿ DL/Portaria nº 109/2021- DOE nº 34.482, de 15/04/2021, fl.01 e 16 ¿ Prestação de serviços de forma Eventual e Gestão de segurança e ativos de rede. Arti</t>
+          <t>Reforço da 2021NE000476 - 2º Aditivo ao Termo de Contrato nº 005/2019-SEAS. Serviços de Acesso à Internet por Fibra Ótica com garantia de 100% em download e upload, para atender as necessidades da SEA</t>
         </is>
       </c>
     </row>
@@ -5474,12 +5474,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2021NE0000536</t>
+          <t>2021NE0000538</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>5/2019</t>
+          <t>3/2021</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5488,7 +5488,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>52267.48</v>
+        <v>36173.2</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Reforço da 2021NE000476 - 2º Aditivo ao Termo de Contrato nº 005/2019-SEAS. Serviços de Acesso à Internet por Fibra Ótica com garantia de 100% em download e upload, para atender as necessidades da SEA</t>
+          <t>Reforço da 2021NE000316 - Contrato nº 03/2021 ¿ DL/Portaria nº 109/2021- DOE nº 34.482, de 15/04/2021, fl.01 e 16 ¿ Prestação de serviços de forma Eventual e Gestão de segurança e ativos de rede. Arti</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5530,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2021NE0000745</t>
+          <t>2021NE0000744</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>6000</v>
+        <v>166272.75</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Anulação de saldo remanescente do contrato nº 01/2021- referente aos meses de fevereiro a setembro/2021 para ajuste orçamentário do exercício 2021</t>
+          <t>Ajuste</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2021NE0000744</t>
+          <t>2021NE0000745</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>166272.75</v>
+        <v>6000</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ajuste</t>
+          <t>Anulação de saldo remanescente do contrato nº 01/2021- referente aos meses de fevereiro a setembro/2021 para ajuste orçamentário do exercício 2021</t>
         </is>
       </c>
     </row>
@@ -5668,12 +5668,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2025NE0000342</t>
+          <t>2025NE0000341</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5/2024</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>58313.26</v>
+        <v>71837.72</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5691,19 +5691,19 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Contratação de empresa prestadora de serviços de tecnologia da informação, para atender as necessidades desta SEAS.</t>
+          <t>Contrato de prestação de serviços de processamento de dados para a geração de relação de benefícios e gestão das entregas do cartão emergencial a famílias com vulnerabilidade social. TC: 0012/2021 AD:</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2025NE0000341</t>
+          <t>2025NE0000342</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>5/2024</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5712,7 +5712,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>71837.72</v>
+        <v>58313.26</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -5721,21 +5721,17 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Contrato de prestação de serviços de processamento de dados para a geração de relação de benefícios e gestão das entregas do cartão emergencial a famílias com vulnerabilidade social. TC: 0012/2021 AD:</t>
+          <t>Contratação de empresa prestadora de serviços de tecnologia da informação, para atender as necessidades desta SEAS.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2020NE00014</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>3/2016</t>
-        </is>
-      </c>
+          <t>2020NE00016</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
       <c r="C180" t="inlineStr">
         <is>
           <t>14/01/2020</t>
@@ -5751,7 +5747,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS.</t>
+          <t>Anulação da NE nº 0014/2020, por erro de descrição.</t>
         </is>
       </c>
     </row>
@@ -5788,10 +5784,14 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2020NE00016</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr"/>
+          <t>2020NE00014</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>3/2016</t>
+        </is>
+      </c>
       <c r="C182" t="inlineStr">
         <is>
           <t>14/01/2020</t>
@@ -5807,14 +5807,14 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Anulação da NE nº 0014/2020, por erro de descrição.</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2024NE0000843</t>
+          <t>2024NE0000844</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -5824,7 +5824,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>37251.14</v>
+        <v>17436.36</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2024NE0000844</t>
+          <t>2024NE0000843</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>17436.36</v>
+        <v>37251.14</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -5948,10 +5948,14 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2019NE00028</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr"/>
+          <t>2019NE00010</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>3/2016</t>
+        </is>
+      </c>
       <c r="C188" t="inlineStr">
         <is>
           <t>13/01/2019</t>
@@ -5967,21 +5971,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Anulação da Ne nº 010/2018, por erro de descrição.</t>
+          <t>Serviços de Licenciamento de Softwares, Licença de Uso de Sistema de Protocolo em Plataforma Web.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2019NE00010</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>3/2016</t>
-        </is>
-      </c>
+          <t>2019NE00028</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr">
         <is>
           <t>13/01/2019</t>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Serviços de Licenciamento de Softwares, Licença de Uso de Sistema de Protocolo em Plataforma Web.</t>
+          <t>Anulação da Ne nº 010/2018, por erro de descrição.</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2015NE00515</t>
+          <t>2015NE00512</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>8701.379999999999</v>
+        <v>9009.780000000001</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6259,14 +6259,14 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Termo de Contrato 03/2014</t>
+          <t>Empenho de contrato: importado manualmente em 21/09/2015</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2015NE00512</t>
+          <t>2015NE00515</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6280,7 +6280,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>9009.780000000001</v>
+        <v>8701.379999999999</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Empenho de contrato: importado manualmente em 21/09/2015</t>
+          <t>Termo de Contrato 03/2014</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2023NE0000816</t>
+          <t>2023NE0000818</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>5/2019</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>27970.49</v>
+        <v>6295.05</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
+          <t xml:space="preserve">Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para a publicação de informações, noticias, vídeos e imagens website. TC: 0007/2021 AD: </t>
         </is>
       </c>
     </row>
@@ -6386,12 +6386,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2023NE0000818</t>
+          <t>2023NE0000816</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>5/2019</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>6295.05</v>
+        <v>27970.49</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para a publicação de informações, noticias, vídeos e imagens website. TC: 0007/2021 AD: </t>
+          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
         </is>
       </c>
     </row>
@@ -6498,12 +6498,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2025NE0000162</t>
+          <t>2025NE0000164</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>5/2024</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>143675.44</v>
+        <v>58313.26</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6521,19 +6521,19 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Contrato de prestação de serviços de processamento de dados para a geração de relação de benefícios e gestão das entregas do cartão emergencial a famílias com vulnerabilidade social. TC: 0012/2021 AD:</t>
+          <t>Contratação de empresa especializada em serviços de tecnologia da informação, para atender as necessidades desta SEAS.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2025NE0000164</t>
+          <t>2025NE0000162</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>5/2024</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>58313.26</v>
+        <v>143675.44</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada em serviços de tecnologia da informação, para atender as necessidades desta SEAS.</t>
+          <t>Contrato de prestação de serviços de processamento de dados para a geração de relação de benefícios e gestão das entregas do cartão emergencial a famílias com vulnerabilidade social. TC: 0012/2021 AD:</t>
         </is>
       </c>
     </row>
@@ -6614,10 +6614,14 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2017NE00094</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr"/>
+          <t>2017NE00095</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>3/2016</t>
+        </is>
+      </c>
       <c r="C211" t="inlineStr">
         <is>
           <t>09/03/2017</t>
@@ -6633,21 +6637,17 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Anulação que se faz para correção na descrição da NE 00074.</t>
+          <t>SERVIÇOS DE LICENCIAMENTO DE SOFTWARES, LICENÇA DE USO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2017NE00095</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>3/2016</t>
-        </is>
-      </c>
+          <t>2017NE00094</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
         <is>
           <t>09/03/2017</t>
@@ -6663,19 +6663,19 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LICENCIAMENTO DE SOFTWARES, LICENÇA DE USO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB</t>
+          <t>Anulação que se faz para correção na descrição da NE 00074.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2015NE00015</t>
+          <t>2015NE00049</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>49/2010</t>
+          <t>3/2014</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>11952</v>
+        <v>26104.14</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Cobertura Financeira 2015</t>
+          <t>Termo de Contrato nº 03/2014</t>
         </is>
       </c>
     </row>
@@ -6730,12 +6730,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2015NE00049</t>
+          <t>2015NE00015</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>3/2014</t>
+          <t>49/2010</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6744,7 +6744,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>26104.14</v>
+        <v>11952</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Termo de Contrato nº 03/2014</t>
+          <t>Cobertura Financeira 2015</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2022NE0000769</t>
+          <t>2022NE0000768</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>5/2019</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1167.84</v>
+        <v>28452.73</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -6895,19 +6895,19 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reforço da Nota de Empenho 2022NE0000044. Saldo - 1º Termo Aditivo ao Contrato nº 001/2021-SEAS. Objeto: Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de </t>
+          <t>REFORÇO DA NE. 000569/2022 3º Termo Aditivo ao Contrato nº 005/2019-SEAS. Objeto: Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manuten</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2022NE0000768</t>
+          <t>2022NE0000769</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>5/2019</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>28452.73</v>
+        <v>1167.84</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -6925,19 +6925,19 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>REFORÇO DA NE. 000569/2022 3º Termo Aditivo ao Contrato nº 005/2019-SEAS. Objeto: Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manuten</t>
+          <t xml:space="preserve">Reforço da Nota de Empenho 2022NE0000044. Saldo - 1º Termo Aditivo ao Contrato nº 001/2021-SEAS. Objeto: Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de </t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2024NE0000305</t>
+          <t>2024NE0000303</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>5/2019</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>4196.7</v>
+        <v>28934.98</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -6955,28 +6955,24 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para a publicação de informações, noticias, vídeos e imagens website. TC: 0007/2021 AD: </t>
+          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2024NE0000304</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>1/2021</t>
-        </is>
-      </c>
+          <t>2024NE0000300</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
         <is>
           <t>07/05/2024</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>2462.98</v>
+        <v>20653.32</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -6985,24 +6981,28 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada n prestação dos serviços de licença de uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS, pelo período de 12 Meses. TC: 0001/2021 AD: 03.</t>
+          <t xml:space="preserve">Anulação do saldo remanescente do TC.03/2021 AD 02, pelo encerramento do mesmo Prazo de Vigência: 05/2023 - 05/2024 Fundamento Legal: Dispensa de Licitação nº 109/2021, de acordo com Art.24; XVI; Lei </t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2024NE0000300</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr"/>
+          <t>2024NE0000304</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>1/2021</t>
+        </is>
+      </c>
       <c r="C224" t="inlineStr">
         <is>
           <t>07/05/2024</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>20653.32</v>
+        <v>2462.98</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7011,19 +7011,19 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anulação do saldo remanescente do TC.03/2021 AD 02, pelo encerramento do mesmo Prazo de Vigência: 05/2023 - 05/2024 Fundamento Legal: Dispensa de Licitação nº 109/2021, de acordo com Art.24; XVI; Lei </t>
+          <t>Contratação de empresa especializada n prestação dos serviços de licença de uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS, pelo período de 12 Meses. TC: 0001/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2024NE0000303</t>
+          <t>2024NE0000305</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>5/2019</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>28934.98</v>
+        <v>4196.7</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7041,19 +7041,19 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
+          <t xml:space="preserve">Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para a publicação de informações, noticias, vídeos e imagens website. TC: 0007/2021 AD: </t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2017NE00217</t>
+          <t>2017NE00216</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>15936</v>
+        <v>1948.6</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE MANUTENÇÃO EM EQUIPAMENTOS DE INFORMATICA</t>
+          <t>Sistema de informação compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem website.</t>
         </is>
       </c>
     </row>
@@ -7108,12 +7108,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2017NE00216</t>
+          <t>2017NE00217</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1948.6</v>
+        <v>15936</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Sistema de informação compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem website.</t>
+          <t>SERVIÇOS DE MANUTENÇÃO EM EQUIPAMENTOS DE INFORMATICA</t>
         </is>
       </c>
     </row>
@@ -7164,12 +7164,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2023NE0000763</t>
+          <t>2023NE0000760</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>3/2021</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>2098.35</v>
+        <v>14486.94</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7187,19 +7187,19 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para a publicação de informações, noticias, vídeos e imagens website. TC: 0007/2021 AD: </t>
+          <t xml:space="preserve">Contratação de empresa especializada na prestação de serviços de manutenção de PROXY, serviço de segurança da informação, serviço de regras de acesso e serviços de FAREWALL em relação a internet. TC: </t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2023NE0000759</t>
+          <t>2023NE0000762</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>5/2019</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -7208,7 +7208,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>14467.49</v>
+        <v>1231.49</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7217,19 +7217,19 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
+          <t>Contratação de empresa especializada n prestação dos serviços de licença de uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS, pelo período de 12 Meses. TC: 001/2021 AD: 02.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2023NE0000762</t>
+          <t>2023NE0000759</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>5/2019</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1231.49</v>
+        <v>14467.49</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7247,19 +7247,19 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada n prestação dos serviços de licença de uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS, pelo período de 12 Meses. TC: 001/2021 AD: 02.</t>
+          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2023NE0000760</t>
+          <t>2023NE0000763</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>3/2021</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>14486.94</v>
+        <v>2098.35</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada na prestação de serviços de manutenção de PROXY, serviço de segurança da informação, serviço de regras de acesso e serviços de FAREWALL em relação a internet. TC: </t>
+          <t xml:space="preserve">Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para a publicação de informações, noticias, vídeos e imagens website. TC: 0007/2021 AD: </t>
         </is>
       </c>
     </row>
@@ -7344,10 +7344,14 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2019NE00221</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr"/>
+          <t>2019NE00222</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>10/2016</t>
+        </is>
+      </c>
       <c r="C236" t="inlineStr">
         <is>
           <t>06/08/2019</t>
@@ -7363,7 +7367,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Anulação da NE nº 220/2019, por erro de descrição.</t>
+          <t>3º Termo Aditivo ao Contrato nº 010/2016-SEAS. Objeto: Serviços de Licença e Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para publicação de informações, no</t>
         </is>
       </c>
     </row>
@@ -7400,14 +7404,10 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2019NE00222</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>10/2016</t>
-        </is>
-      </c>
+          <t>2019NE00221</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
       <c r="C238" t="inlineStr">
         <is>
           <t>06/08/2019</t>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>3º Termo Aditivo ao Contrato nº 010/2016-SEAS. Objeto: Serviços de Licença e Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para publicação de informações, no</t>
+          <t>Anulação da NE nº 220/2019, por erro de descrição.</t>
         </is>
       </c>
     </row>
@@ -7460,14 +7460,10 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2016NE00468</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>3/2014</t>
-        </is>
-      </c>
+          <t>2016NE00465</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr">
         <is>
           <t>06/04/2016</t>
@@ -7483,14 +7479,14 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0220/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
+          <t>Anulação da NE 464/2016, em virtude de descrição incorreta.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2016NE00469</t>
+          <t>2016NE00467</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -7504,7 +7500,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>8701.379999999999</v>
+        <v>9009.780000000001</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -7513,21 +7509,17 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0066/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
+          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0219/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2016NE00466</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>3/2014</t>
-        </is>
-      </c>
+          <t>2016NE00464</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
       <c r="C242" t="inlineStr">
         <is>
           <t>06/04/2016</t>
@@ -7543,17 +7535,21 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0065/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
+          <t>Reconhecimento da Divida - RD nº 119/2016: Necessidade de compra de KITS, modelagem e corte e costura-malharia, para realização dos cursos nos Centros de Convivência da Familia e do Idoso Aparecida,CE</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2016NE00464</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr"/>
+          <t>2016NE00466</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>3/2014</t>
+        </is>
+      </c>
       <c r="C243" t="inlineStr">
         <is>
           <t>06/04/2016</t>
@@ -7569,14 +7565,14 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Reconhecimento da Divida - RD nº 119/2016: Necessidade de compra de KITS, modelagem e corte e costura-malharia, para realização dos cursos nos Centros de Convivência da Familia e do Idoso Aparecida,CE</t>
+          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0065/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2016NE00467</t>
+          <t>2016NE00469</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7590,7 +7586,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>9009.780000000001</v>
+        <v>8701.379999999999</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -7599,17 +7595,21 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0219/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
+          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0066/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2016NE00465</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr"/>
+          <t>2016NE00468</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>3/2014</t>
+        </is>
+      </c>
       <c r="C245" t="inlineStr">
         <is>
           <t>06/04/2016</t>
@@ -7625,19 +7625,19 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Anulação da NE 464/2016, em virtude de descrição incorreta.</t>
+          <t xml:space="preserve">Reconhecimento da Divida - RD nº 0220/2016: Termo de Contrato n. 003/2014-SEAS-Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados dedicado para </t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2024NE0000087</t>
+          <t>2024NE0000086</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>5/2019</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7646,7 +7646,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>2462.98</v>
+        <v>28934.98</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada n prestação dos serviços de licença de uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS, pelo período de 12 Meses. TC: 0001/2021 AD: 03.</t>
+          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
         </is>
       </c>
     </row>
@@ -7692,12 +7692,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2024NE0000086</t>
+          <t>2024NE0000087</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>5/2019</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>28934.98</v>
+        <v>2462.98</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -7715,14 +7715,14 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
+          <t>Contratação de empresa especializada n prestação dos serviços de licença de uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS, pelo período de 12 Meses. TC: 0001/2021 AD: 03.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2019NE00433</t>
+          <t>2019NE00432</t>
         </is>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -7732,7 +7732,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>128420.42</v>
+        <v>72555.02</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Anulação Parcial da NE, SALDO CT 16/17 - 2.º TA Natureza da Despesa: 33904003 - Hospedagem de Sistemas. - Natureza da Despesa: 33904003 - Hospedagem de Sistemas, em obediência ao Decreto nº 41.554, de</t>
+          <t>Anulação total da NE, SALDO CT 16/17 -1.º TA - Natureza da Despesa: 33904003 - Hospedagem de Sistemas, em obediência ao Decreto nº .554, de 26/11/2019, que dispõe sobre o encerramento da execução orça</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2019NE00432</t>
+          <t>2019NE00433</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>72555.02</v>
+        <v>128420.42</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Anulação total da NE, SALDO CT 16/17 -1.º TA - Natureza da Despesa: 33904003 - Hospedagem de Sistemas, em obediência ao Decreto nº .554, de 26/11/2019, que dispõe sobre o encerramento da execução orça</t>
+          <t>Anulação Parcial da NE, SALDO CT 16/17 - 2.º TA Natureza da Despesa: 33904003 - Hospedagem de Sistemas. - Natureza da Despesa: 33904003 - Hospedagem de Sistemas, em obediência ao Decreto nº 41.554, de</t>
         </is>
       </c>
     </row>
@@ -8032,12 +8032,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2015NE00005</t>
+          <t>2015NE00007</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>11/2014</t>
+          <t>49/2010</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>4500</v>
+        <v>11952</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -8055,19 +8055,19 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Serviços de Licenças de softwares</t>
+          <t>Prestação de serviços de informática</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2015NE00007</t>
+          <t>2015NE00005</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>49/2010</t>
+          <t>11/2014</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>11952</v>
+        <v>4500</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -8085,14 +8085,14 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Prestação de serviços de informática</t>
+          <t>Serviços de Licenças de softwares</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2017NE00468</t>
+          <t>2017NE00461</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -8122,14 +8122,10 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2017NE00466</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>16/2017</t>
-        </is>
-      </c>
+          <t>2017NE00465</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
       <c r="C263" t="inlineStr">
         <is>
           <t>04/09/2017</t>
@@ -8145,7 +8141,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>SERVIÇO DE DESENVOLVIMENTO E HOSPEDAGEM DE SISTEMAS DE INFORMAÇÕES PARA IMPLANTAÇÃO DAS PLATAFORMAS ELETRÔNICAS SOBRE O COFINANCIAMENTO ESTADUAL E MARCO REGULATÓRIO DAS ORGANIZAÇÕES DA SOCIEDADE CIVIL</t>
+          <t>ANULAÇÃO DA NE Nº 461/2017, POR ERRO DE DESCRIÇÃO.</t>
         </is>
       </c>
     </row>
@@ -8178,10 +8174,14 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2017NE00465</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr"/>
+          <t>2017NE00466</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>16/2017</t>
+        </is>
+      </c>
       <c r="C265" t="inlineStr">
         <is>
           <t>04/09/2017</t>
@@ -8197,14 +8197,14 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE Nº 461/2017, POR ERRO DE DESCRIÇÃO.</t>
+          <t>SERVIÇO DE DESENVOLVIMENTO E HOSPEDAGEM DE SISTEMAS DE INFORMAÇÕES PARA IMPLANTAÇÃO DAS PLATAFORMAS ELETRÔNICAS SOBRE O COFINANCIAMENTO ESTADUAL E MARCO REGULATÓRIO DAS ORGANIZAÇÕES DA SOCIEDADE CIVIL</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2017NE00461</t>
+          <t>2017NE00468</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -8320,17 +8320,21 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2016NE00029</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr"/>
+          <t>2016NE00022</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2/2016</t>
+        </is>
+      </c>
       <c r="C270" t="inlineStr">
         <is>
           <t>04/01/2016</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>9000</v>
+        <v>9492.190000000001</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -8339,19 +8343,19 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Anulação que se faz a n.e. 00020, por erro de digitação na vigência do contrato</t>
+          <t>Termo de Contrato a ser firmado. Objeto: Contratação, por dispensa de licitação, compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem para armazenamento de dados.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2016NE00020</t>
+          <t>2016NE00019</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -8360,7 +8364,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>9000</v>
+        <v>23904</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -8369,19 +8373,19 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Termo de Contrato a ser firmado. Objeto: Contratação de pessoa jurídica especializada na Prestação de Serviços de execução do Sistema de Protocolo em Plataforma Web (SPROWEB), para atender as desta Se</t>
+          <t>Termo de Contrato a ser firmado. Objeto: Contratação, por dispensa de licitação, de pessoa jurídica especializada em Serviços Técnicos em Informática, para atender as necessidades desta Secretaria e s</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2016NE00019</t>
+          <t>2016NE00020</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -8390,7 +8394,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>23904</v>
+        <v>9000</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -8399,28 +8403,24 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Termo de Contrato a ser firmado. Objeto: Contratação, por dispensa de licitação, de pessoa jurídica especializada em Serviços Técnicos em Informática, para atender as necessidades desta Secretaria e s</t>
+          <t>Termo de Contrato a ser firmado. Objeto: Contratação de pessoa jurídica especializada na Prestação de Serviços de execução do Sistema de Protocolo em Plataforma Web (SPROWEB), para atender as desta Se</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2016NE00022</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>2/2016</t>
-        </is>
-      </c>
+          <t>2016NE00029</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
       <c r="C273" t="inlineStr">
         <is>
           <t>04/01/2016</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>9492.190000000001</v>
+        <v>9000</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Termo de Contrato a ser firmado. Objeto: Contratação, por dispensa de licitação, compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem para armazenamento de dados.</t>
+          <t>Anulação que se faz a n.e. 00020, por erro de digitação na vigência do contrato</t>
         </is>
       </c>
     </row>
@@ -8608,12 +8608,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2024NE0000474</t>
+          <t>2024NE0000472</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>5/2019</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>3004.64</v>
+        <v>14467.49</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para a publicação de informações, noticias, vídeos e imagens website. TC: 0007/2021 AD: </t>
+          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
         </is>
       </c>
     </row>
@@ -8668,12 +8668,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2024NE0000472</t>
+          <t>2024NE0000474</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>5/2019</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>14467.49</v>
+        <v>3004.64</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
+          <t xml:space="preserve">Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para a publicação de informações, noticias, vídeos e imagens website. TC: 0007/2021 AD: </t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2022NE0000259</t>
+          <t>2022NE0000257</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -8738,7 +8738,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>817.9</v>
+        <v>817.14</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -8747,14 +8747,14 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Execução de sistemas SISTEMA: Sist. de Recursos Humanos e Folha Faturamento mínimo por folha - até 200 funcionários processados, conforme PARECER Nº 331/2021 – ASSEJUR/SEAS</t>
+          <t>Execução de sistemas SISTEMA: Sist. de Recursos Humanos e Folha Faturamento mínimo por folha - até 200 funcionários processados, conforme PARECER Nº 329/2021 – ASSEJUR/SEAS</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2022NE0000257</t>
+          <t>2022NE0000259</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -8764,7 +8764,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>817.14</v>
+        <v>817.9</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -8773,19 +8773,19 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Execução de sistemas SISTEMA: Sist. de Recursos Humanos e Folha Faturamento mínimo por folha - até 200 funcionários processados, conforme PARECER Nº 329/2021 – ASSEJUR/SEAS</t>
+          <t>Execução de sistemas SISTEMA: Sist. de Recursos Humanos e Folha Faturamento mínimo por folha - até 200 funcionários processados, conforme PARECER Nº 331/2021 – ASSEJUR/SEAS</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2022NE0000023</t>
+          <t>2022NE0000041</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>5/2019</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -8794,7 +8794,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>52267.48</v>
+        <v>3503.52</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -8803,19 +8803,19 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>PRORROGAÇÃO DE PRAZO DE VIGÊNCIA CONTRATUAL POR MAIS 12 MESES.</t>
+          <t>1º Aditivo ao Termo de Contrato 01/2021 Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS, pelo pe</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2022NE0000021</t>
+          <t>2022NE0000038</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>16/2017</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>2210.93</v>
+        <v>50845.92</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -8833,28 +8833,24 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Prestação de serviços de execução de Sistema de Protocolo em plataforma WEB (SPROWEB), objetivando o controle e acompanhamento do registro de todos os doumentos ou processos desta SEAS.</t>
+          <t>4º Termo Aditivo ao Contrato nº 016/2017 - SEAS. Objeto do Contrato: Serviço de Desenvolvimento e Hospedagem de Sistemas de Informações para Implantação das Plataformas Eletrônicas sobre o Financiamen</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2022NE0000024</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>7/2021</t>
-        </is>
-      </c>
+          <t>2022NE0000040</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
       <c r="C288" t="inlineStr">
         <is>
           <t>03/01/2022</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>7580.76</v>
+        <v>3503.52</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -8863,19 +8859,19 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para publicação de informações notícias, vídeos e imagens website.</t>
+          <t>Anulação da NE nº 00029/2022, por a erro de descrição.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2022NE0000026</t>
+          <t>2022NE0000028</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>3/2021</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -8884,7 +8880,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>296662.22</v>
+        <v>47434</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -8893,7 +8889,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Contrato de Prestação de serviços de processamento de dados para geração de relação de benefícios e gestão das entregas do cartão Auxílio Emergencial a famílias com vulnerabilidade social,</t>
+          <t>Contrato nº 03/2021 – DL/Portaria nº 109/2021- DOE nº 34.482, de 15/04/2021, fl.01 e 16 – Prestação de serviços de forma Eventual e Gestão de segurança e ativos de rede. Artigo 16 - Lei 8.666/93</t>
         </is>
       </c>
     </row>
@@ -8930,12 +8926,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2022NE0000028</t>
+          <t>2022NE0000026</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>3/2021</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -8944,7 +8940,7 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>47434</v>
+        <v>296662.22</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -8953,24 +8949,28 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Contrato nº 03/2021 – DL/Portaria nº 109/2021- DOE nº 34.482, de 15/04/2021, fl.01 e 16 – Prestação de serviços de forma Eventual e Gestão de segurança e ativos de rede. Artigo 16 - Lei 8.666/93</t>
+          <t>Contrato de Prestação de serviços de processamento de dados para geração de relação de benefícios e gestão das entregas do cartão Auxílio Emergencial a famílias com vulnerabilidade social,</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2022NE0000040</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr"/>
+          <t>2022NE0000024</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>7/2021</t>
+        </is>
+      </c>
       <c r="C292" t="inlineStr">
         <is>
           <t>03/01/2022</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>3503.52</v>
+        <v>7580.76</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -8979,19 +8979,19 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Anulação da NE nº 00029/2022, por a erro de descrição.</t>
+          <t>Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para publicação de informações notícias, vídeos e imagens website.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2022NE0000038</t>
+          <t>2022NE0000021</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>16/2017</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>50845.92</v>
+        <v>2210.93</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -9009,19 +9009,19 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>4º Termo Aditivo ao Contrato nº 016/2017 - SEAS. Objeto do Contrato: Serviço de Desenvolvimento e Hospedagem de Sistemas de Informações para Implantação das Plataformas Eletrônicas sobre o Financiamen</t>
+          <t>Prestação de serviços de execução de Sistema de Protocolo em plataforma WEB (SPROWEB), objetivando o controle e acompanhamento do registro de todos os doumentos ou processos desta SEAS.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2022NE0000041</t>
+          <t>2022NE0000023</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>5/2019</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -9030,7 +9030,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>3503.52</v>
+        <v>52267.48</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>1º Aditivo ao Termo de Contrato 01/2021 Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS, pelo pe</t>
+          <t>PRORROGAÇÃO DE PRAZO DE VIGÊNCIA CONTRATUAL POR MAIS 12 MESES.</t>
         </is>
       </c>
     </row>
@@ -9076,7 +9076,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2015NE00754</t>
+          <t>2015NE00753</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -9086,7 +9086,7 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>3944.81</v>
+        <v>779.5</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Reconhecimento de Divida folha de informação de exercicio anteriores nº 0121/2015. Prestação de Serviços eventuais (reparação e manutenção de computadores e equipamentos , referente ao mês de outubro/</t>
+          <t>Reconhecimento de Divida folha de informação de exercicio anteriores nº 0119/2015. Prestação de Serviços de licença de uso de informação do sistema protocolo Delphi cessão em uso do sproweb tramitação</t>
         </is>
       </c>
     </row>
@@ -9132,7 +9132,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2015NE00753</t>
+          <t>2015NE00754</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>779.5</v>
+        <v>3944.81</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -9151,14 +9151,14 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Reconhecimento de Divida folha de informação de exercicio anteriores nº 0119/2015. Prestação de Serviços de licença de uso de informação do sistema protocolo Delphi cessão em uso do sproweb tramitação</t>
+          <t>Reconhecimento de Divida folha de informação de exercicio anteriores nº 0121/2015. Prestação de Serviços eventuais (reparação e manutenção de computadores e equipamentos , referente ao mês de outubro/</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2019NE00217</t>
+          <t>2019NE00218</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -9168,7 +9168,7 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>19888.2</v>
+        <v>2473.35</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -9177,24 +9177,28 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Anulação da NE nº 201/2019 por erro de descrição.</t>
+          <t>Anulação da NE nº 196/2019, por erro de descrição.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2019NE00210</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr"/>
+          <t>2019NE00219</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>5/2019</t>
+        </is>
+      </c>
       <c r="C300" t="inlineStr">
         <is>
           <t>02/08/2019</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>696.74</v>
+        <v>26517.6</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -9203,28 +9207,24 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Anulação saldo remanescente do contrato 03/16 SPROWEB</t>
+          <t xml:space="preserve">Termo de Contrato nº 005/2019 - SEAS. Objeto: Contratação de Pessoa Jurídica Especializada no Serviços de Acesso a Internet por Fibra Ótica com com garantia de 100% em download e upload, para atender </t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2019NE00219</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>5/2019</t>
-        </is>
-      </c>
+          <t>2019NE00210</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr"/>
       <c r="C301" t="inlineStr">
         <is>
           <t>02/08/2019</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>26517.6</v>
+        <v>696.74</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -9233,14 +9233,14 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Termo de Contrato nº 005/2019 - SEAS. Objeto: Contratação de Pessoa Jurídica Especializada no Serviços de Acesso a Internet por Fibra Ótica com com garantia de 100% em download e upload, para atender </t>
+          <t>Anulação saldo remanescente do contrato 03/16 SPROWEB</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2019NE00218</t>
+          <t>2019NE00217</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>2473.35</v>
+        <v>19888.2</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -9259,14 +9259,14 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Anulação da NE nº 196/2019, por erro de descrição.</t>
+          <t>Anulação da NE nº 201/2019 por erro de descrição.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2017NE00430</t>
+          <t>2017NE00410</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>3819.81</v>
+        <v>540.98</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -9289,14 +9289,14 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Serviços de Licença de Uso de Sistema de Informática, Compreendendo a Disponibilização de Gestor de Conteúdo Web, para Publicação de Informações, Notícias, Vídeos e Imagens Website.</t>
+          <t>SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMÁTICA, DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2017NE00410</t>
+          <t>2017NE00430</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>540.98</v>
+        <v>3819.81</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMÁTICA, DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB</t>
+          <t>Serviços de Licença de Uso de Sistema de Informática, Compreendendo a Disponibilização de Gestor de Conteúdo Web, para Publicação de Informações, Notícias, Vídeos e Imagens Website.</t>
         </is>
       </c>
     </row>
@@ -9356,10 +9356,14 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2017NE00071</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr"/>
+          <t>2017NE00072</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>3/2016</t>
+        </is>
+      </c>
       <c r="C306" t="inlineStr">
         <is>
           <t>02/03/2017</t>
@@ -9375,17 +9379,21 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Anulação da NE 065/2017, em virtude de descrição incorreta</t>
+          <t>SERVIÇOS DE LICENCIAMENTO DE SOFTWARES, LICENÇA DE USO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2017NE00073</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr"/>
+          <t>2017NE00074</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>3/2016</t>
+        </is>
+      </c>
       <c r="C307" t="inlineStr">
         <is>
           <t>02/03/2017</t>
@@ -9401,21 +9409,17 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Anulação da NE 072/2017, em virtude de descrição incorreta</t>
+          <t>SERVIÇOS DE LICENCIAMENTO DE SOFTWARES, LICENÇA DE USO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2017NE00074</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>3/2016</t>
-        </is>
-      </c>
+          <t>2017NE00073</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr"/>
       <c r="C308" t="inlineStr">
         <is>
           <t>02/03/2017</t>
@@ -9431,21 +9435,17 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LICENCIAMENTO DE SOFTWARES, LICENÇA DE USO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB</t>
+          <t>Anulação da NE 072/2017, em virtude de descrição incorreta</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2017NE00072</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>3/2016</t>
-        </is>
-      </c>
+          <t>2017NE00071</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr"/>
       <c r="C309" t="inlineStr">
         <is>
           <t>02/03/2017</t>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LICENCIAMENTO DE SOFTWARES, LICENÇA DE USO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB</t>
+          <t>Anulação da NE 065/2017, em virtude de descrição incorreta</t>
         </is>
       </c>
     </row>
@@ -9498,14 +9498,10 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2018NE00129</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>3/2014</t>
-        </is>
-      </c>
+          <t>2018NE00137</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr"/>
       <c r="C311" t="inlineStr">
         <is>
           <t>02/02/2018</t>
@@ -9521,28 +9517,24 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LINK DE COMUNICAÇÃO PARA ATENDER AS NECESSIDADES DA SEAS.</t>
+          <t>Anulação da NE 0136/2018, em virtude de Natureza incorreta.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2018NE00130</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>10/2016</t>
-        </is>
-      </c>
+          <t>2018NE00135</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr"/>
       <c r="C312" t="inlineStr">
         <is>
           <t>02/02/2018</t>
         </is>
       </c>
       <c r="D312" t="n">
-        <v>10685.99</v>
+        <v>46783.8</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -9551,7 +9543,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Serviços de Licença de Uso de Sistema de Informática, Compreendendo a Disponibilização de Gestor de Conteúdo Web, para Publicação de Informações, Notícias, Vídeos e Imagens Website.</t>
+          <t>Anulação da NE 0129/2018, me virtude de descrição incorreta.</t>
         </is>
       </c>
     </row>
@@ -9588,17 +9580,21 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2018NE00135</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr"/>
+          <t>2018NE00130</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>10/2016</t>
+        </is>
+      </c>
       <c r="C314" t="inlineStr">
         <is>
           <t>02/02/2018</t>
         </is>
       </c>
       <c r="D314" t="n">
-        <v>46783.8</v>
+        <v>10685.99</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -9607,17 +9603,21 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Anulação da NE 0129/2018, me virtude de descrição incorreta.</t>
+          <t>Serviços de Licença de Uso de Sistema de Informática, Compreendendo a Disponibilização de Gestor de Conteúdo Web, para Publicação de Informações, Notícias, Vídeos e Imagens Website.</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2018NE00137</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr"/>
+          <t>2018NE00129</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>3/2014</t>
+        </is>
+      </c>
       <c r="C315" t="inlineStr">
         <is>
           <t>02/02/2018</t>
@@ -9633,7 +9633,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Anulação da NE 0136/2018, em virtude de Natureza incorreta.</t>
+          <t>SERVIÇOS DE LINK DE COMUNICAÇÃO PARA ATENDER AS NECESSIDADES DA SEAS.</t>
         </is>
       </c>
     </row>
@@ -9670,12 +9670,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2024NE0000006</t>
+          <t>2024NE0000008</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>5/2019</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -9684,7 +9684,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>28934.98</v>
+        <v>4196.7</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -9693,19 +9693,19 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
+          <t xml:space="preserve">Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para a publicação de informações, noticias, vídeos e imagens website. TC: 0007/2021 AD: </t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2024NE0000005</t>
+          <t>2024NE0000007</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>3/2021</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -9714,7 +9714,7 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>22095.48</v>
+        <v>1231.49</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de empresa especializada na prestação de serviços de manutenção de PROXY, serviço de segurança da informação, serviço de regras de acesso e serviços de FAREWALL em relação a internet. TC: </t>
+          <t>Contratação de empresa especializada n prestação dos serviços de licença de uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS, pelo período de 12 Meses. TC: 0001/2021 AD: 02.</t>
         </is>
       </c>
     </row>
@@ -9760,12 +9760,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2024NE0000007</t>
+          <t>2024NE0000005</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>3/2021</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>1231.49</v>
+        <v>22095.48</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -9783,19 +9783,19 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Contratação de empresa especializada n prestação dos serviços de licença de uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS, pelo período de 12 Meses. TC: 0001/2021 AD: 02.</t>
+          <t xml:space="preserve">Contratação de empresa especializada na prestação de serviços de manutenção de PROXY, serviço de segurança da informação, serviço de regras de acesso e serviços de FAREWALL em relação a internet. TC: </t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2024NE0000008</t>
+          <t>2024NE0000006</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>5/2019</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -9804,7 +9804,7 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>4196.7</v>
+        <v>28934.98</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -9813,19 +9813,19 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para a publicação de informações, noticias, vídeos e imagens website. TC: 0007/2021 AD: </t>
+          <t xml:space="preserve">Contratação de Serviços de rede, contemplando o fornecimento de circuito de transmissão de dados, contemplando manutenção à metromao, através de rede de governo, por meio de fibra ótica, para atender </t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2023NE0000013</t>
+          <t>2023NE0000020</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>1/2021</t>
+          <t>7/2021</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -9834,7 +9834,7 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>1167.84</v>
+        <v>8393.4</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -9843,19 +9843,19 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS, pelo período de 12 meses.</t>
+          <t>Saldo - 1º Termo Aditivo ao Contrato nº 007/2021-SEAS. Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para a publicação de informações,</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2023NE0000014</t>
+          <t>2023NE0000016</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>3/2021</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -9864,7 +9864,7 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>43708.8</v>
+        <v>287613.24</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -9873,19 +9873,19 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Saldo - 1º Aditivo ao Termo de Contrato nº 003/2021-SEAS. Prestação de serviços de manutenção do serviço PROXY, serviço de segurança da informação, serviço de regras de acesso e serviços de FIREWALL e</t>
+          <t>1º Termo Aditivo ao Contrato nº 012/2021-SEAS. Contrato de prestação de serviços de processamento de dados para a geração de relação de benefícios e gestão das entregas do cartão emergencial a família</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2023NE0000016</t>
+          <t>2023NE0000014</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>3/2021</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -9894,7 +9894,7 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>287613.24</v>
+        <v>43708.8</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -9903,19 +9903,19 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>1º Termo Aditivo ao Contrato nº 012/2021-SEAS. Contrato de prestação de serviços de processamento de dados para a geração de relação de benefícios e gestão das entregas do cartão emergencial a família</t>
+          <t>Saldo - 1º Aditivo ao Termo de Contrato nº 003/2021-SEAS. Prestação de serviços de manutenção do serviço PROXY, serviço de segurança da informação, serviço de regras de acesso e serviços de FIREWALL e</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2023NE0000020</t>
+          <t>2023NE0000013</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>7/2021</t>
+          <t>1/2021</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -9924,7 +9924,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>8393.4</v>
+        <v>1167.84</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -9933,28 +9933,24 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Saldo - 1º Termo Aditivo ao Contrato nº 007/2021-SEAS. Serviços de Licença de Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para a publicação de informações,</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS, pelo período de 12 meses.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2020NE00009</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>16/2017</t>
-        </is>
-      </c>
+          <t>2020NE00012</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr"/>
       <c r="C326" t="inlineStr">
         <is>
           <t>02/01/2020</t>
         </is>
       </c>
       <c r="D326" t="n">
-        <v>182237</v>
+        <v>8100.65</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -9963,14 +9959,14 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na Prestação dos Serviços de Desenvolvimento e Hospedagem de Sistemas de Informações para Implantação das Plataformas Eletrônicas sobre o Cofinanciamento Estadual </t>
+          <t>Anulação da NE Nº 11 por erro de digitação na data da Nota de Empenho</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2020NE00008</t>
+          <t>2020NE00011</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -9984,7 +9980,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>741.6</v>
+        <v>8100.65</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -9993,19 +9989,19 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Serviços de Licenciamento de Softwares, Licença de Uso de Sistema de Protocolo em Plataforma Web.</t>
+          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS.</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2020NE00003</t>
+          <t>2020NE00001</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>5/2019</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -10014,7 +10010,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>7562.6</v>
+        <v>66294</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -10023,19 +10019,19 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Serviços de Licença e Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para publicação de informações, notícias, vídeos e imagens website.</t>
+          <t>Contratação de Pessoa Jurídica Especializada no Serviços de Acesso a Internet por Fibra Ótica com com garantia de 100% em download e upload, para atender as necessidades da SEAS e suas Unidades.</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2020NE00001</t>
+          <t>2020NE00003</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>5/2019</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -10044,7 +10040,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>66294</v>
+        <v>7562.6</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -10053,14 +10049,14 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Contratação de Pessoa Jurídica Especializada no Serviços de Acesso a Internet por Fibra Ótica com com garantia de 100% em download e upload, para atender as necessidades da SEAS e suas Unidades.</t>
+          <t>Serviços de Licença e Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para publicação de informações, notícias, vídeos e imagens website.</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2020NE00011</t>
+          <t>2020NE00008</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -10074,7 +10070,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>8100.65</v>
+        <v>741.6</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -10083,24 +10079,28 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Contratação de Empresa Especializada na Prestação dos Serviços de Licença de Uso de Sistema de Informação SPROWEB, para atender as necessidades da SEAS.</t>
+          <t>Serviços de Licenciamento de Softwares, Licença de Uso de Sistema de Protocolo em Plataforma Web.</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2020NE00012</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr"/>
+          <t>2020NE00009</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>16/2017</t>
+        </is>
+      </c>
       <c r="C331" t="inlineStr">
         <is>
           <t>02/01/2020</t>
         </is>
       </c>
       <c r="D331" t="n">
-        <v>8100.65</v>
+        <v>182237</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -10109,19 +10109,19 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Anulação da NE Nº 11 por erro de digitação na data da Nota de Empenho</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na Prestação dos Serviços de Desenvolvimento e Hospedagem de Sistemas de Informações para Implantação das Plataformas Eletrônicas sobre o Cofinanciamento Estadual </t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2019NE00005</t>
+          <t>2019NE00006</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>16/2017</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>4537.56</v>
+        <v>109342.2</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -10139,19 +10139,19 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Serviços de Licença e Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para publicação de informações, notícias, vídeos e imagens website.</t>
+          <t xml:space="preserve">Contratação de Empresa Especializada na Prestação dos Serviços de Desenvolvimento e Hospedagem de Sistemas de Informações para Implantação das Plataformas Eletrônicas sobre o Cofinanciamento Estadual </t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2019NE00003</t>
+          <t>2019NE00004</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>3/2016</t>
+          <t>3/2014</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -10160,7 +10160,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>696.74</v>
+        <v>29862</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -10169,19 +10169,19 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LICENCIAMENTO DE SOFTWARES, LICENÇA DE USO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB.</t>
+          <t>Serviços de Link de Comunicação para Atender as Necessidades da SEAS.</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2019NE00004</t>
+          <t>2019NE00003</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>3/2014</t>
+          <t>3/2016</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -10190,7 +10190,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>29862</v>
+        <v>696.74</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -10199,19 +10199,19 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Serviços de Link de Comunicação para Atender as Necessidades da SEAS.</t>
+          <t>SERVIÇOS DE LICENCIAMENTO DE SOFTWARES, LICENÇA DE USO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB.</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2019NE00006</t>
+          <t>2019NE00005</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>16/2017</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -10220,7 +10220,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>109342.2</v>
+        <v>4537.56</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -10229,28 +10229,24 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contratação de Empresa Especializada na Prestação dos Serviços de Desenvolvimento e Hospedagem de Sistemas de Informações para Implantação das Plataformas Eletrônicas sobre o Cofinanciamento Estadual </t>
+          <t>Serviços de Licença e Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para publicação de informações, notícias, vídeos e imagens website.</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2018NE00051</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>10/2016</t>
-        </is>
-      </c>
+          <t>2018NE00063</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr"/>
       <c r="C336" t="inlineStr">
         <is>
           <t>02/01/2018</t>
         </is>
       </c>
       <c r="D336" t="n">
-        <v>10685.99</v>
+        <v>46783.8</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -10259,14 +10255,14 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Serviços de Licença de Uso de Sistema de Informática, Compreendendo a Disponibilização de Gestor de Conteúdo Web, para Publicação de Informações, Notícias, Vídeos e Imagens Website.</t>
+          <t>Anulação da NE 052/2018, em virtude de descrição incorreta.</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2018NE00064</t>
+          <t>2018NE00052</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -10296,7 +10292,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2018NE00052</t>
+          <t>2018NE00064</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -10326,17 +10322,21 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2018NE00063</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr"/>
+          <t>2018NE00051</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>10/2016</t>
+        </is>
+      </c>
       <c r="C339" t="inlineStr">
         <is>
           <t>02/01/2018</t>
         </is>
       </c>
       <c r="D339" t="n">
-        <v>46783.8</v>
+        <v>10685.99</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -10345,19 +10345,19 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Anulação da NE 052/2018, em virtude de descrição incorreta.</t>
+          <t>Serviços de Licença de Uso de Sistema de Informática, Compreendendo a Disponibilização de Gestor de Conteúdo Web, para Publicação de Informações, Notícias, Vídeos e Imagens Website.</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2017NE00004</t>
+          <t>2017NE00005</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>3/2014</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -10366,7 +10366,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>39989</v>
+        <v>5901.16</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LINK DE COMUNICAÇÃO PARA ATENDER AS NECESSIDADES DA SEAS.</t>
+          <t>SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMATICA, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTICIAS, VIDEOS E IMAGENS WEBSITE.</t>
         </is>
       </c>
     </row>
@@ -10412,12 +10412,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2017NE00005</t>
+          <t>2017NE00004</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>3/2014</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -10426,7 +10426,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>5901.16</v>
+        <v>39989</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -10435,28 +10435,24 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LICENÇA DE USO DE SISTEMA DE INFORMATICA, COMPREENDENDO A DISPONIBILIZAÇÃO DE GESTOR DE CONTEÚDO WEB, PARA PUBLICAÇÃO DE INFORMAÇÕES, NOTICIAS, VIDEOS E IMAGENS WEBSITE.</t>
+          <t>SERVIÇOS DE LINK DE COMUNICAÇÃO PARA ATENDER AS NECESSIDADES DA SEAS.</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2017NE00609</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>10/2016</t>
-        </is>
-      </c>
+          <t>2017NE00631</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr"/>
       <c r="C343" t="inlineStr">
         <is>
           <t>01/12/2017</t>
         </is>
       </c>
       <c r="D343" t="n">
-        <v>1450.58</v>
+        <v>445.46</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -10465,19 +10461,19 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Serviços de Licença de Uso de Sistema de Informática, Compreendendo a Disponibilização de Gestor de Conteúdo Web, para Publicação de Informações, Notícias, Vídeos e Imagens Website.</t>
+          <t>ANULAÇÃO PARCIAL DA NE 095/2017, CONFORME INSTRUÇÃO NORMATIVA Nº 0001/2017-GSEFAZ DE 12 DE DEZEMBRO, EM VIRTUDE DE ENCERRAMENTO DE EXERCÍCIO.</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2017NE00607</t>
+          <t>2017NE00613</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>3/2014</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -10486,7 +10482,7 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>9954</v>
+        <v>3984</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -10495,19 +10491,19 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LINK DE COMUNICAÇÃO PARA ATENDER AS NECESSIDADES DA SEAS.</t>
+          <t>SERVIÇOS DE MANUTENÇÃO EM EQUIPAMENTOS DE INFORMATICA</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2017NE00610</t>
+          <t>2017NE00611</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>3/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -10516,7 +10512,7 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>1607.86</v>
+        <v>487.15</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -10525,7 +10521,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LICENCIAMENTO DE SOFTWARES, LICENÇA DE USO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB</t>
+          <t>Sistema de informação compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem website.</t>
         </is>
       </c>
     </row>
@@ -10558,12 +10554,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2017NE00611</t>
+          <t>2017NE00610</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>3/2016</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -10572,7 +10568,7 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>487.15</v>
+        <v>1607.86</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -10581,19 +10577,19 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Sistema de informação compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem website.</t>
+          <t>SERVIÇOS DE LICENCIAMENTO DE SOFTWARES, LICENÇA DE USO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2017NE00613</t>
+          <t>2017NE00607</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>3/2014</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -10602,7 +10598,7 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>3984</v>
+        <v>9954</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -10611,24 +10607,28 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE MANUTENÇÃO EM EQUIPAMENTOS DE INFORMATICA</t>
+          <t>SERVIÇOS DE LINK DE COMUNICAÇÃO PARA ATENDER AS NECESSIDADES DA SEAS.</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2017NE00631</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr"/>
+          <t>2017NE00609</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>10/2016</t>
+        </is>
+      </c>
       <c r="C349" t="inlineStr">
         <is>
           <t>01/12/2017</t>
         </is>
       </c>
       <c r="D349" t="n">
-        <v>445.46</v>
+        <v>1450.58</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -10637,19 +10637,19 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 095/2017, CONFORME INSTRUÇÃO NORMATIVA Nº 0001/2017-GSEFAZ DE 12 DE DEZEMBRO, EM VIRTUDE DE ENCERRAMENTO DE EXERCÍCIO.</t>
+          <t>Serviços de Licença de Uso de Sistema de Informática, Compreendendo a Disponibilização de Gestor de Conteúdo Web, para Publicação de Informações, Notícias, Vídeos e Imagens Website.</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2016NE00765</t>
+          <t>2016NE00767</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>3/2016</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -10658,7 +10658,7 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>1500</v>
+        <v>454.46</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -10667,24 +10667,28 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Termo de Contrato nº 003/2016-SEAS Objeto: Contratação, por dispensa de licitação, de pessoa jurídica especializada em Licença de uso de Sistema de Informação, para atender as necessidades da Secretar</t>
+          <t>Termo de Contrato nº 02/2016 Objeto: Contratação, por dispensa de licitação, compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem para armazenamento de dados. Val</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2016NE00759</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr"/>
+          <t>2016NE00764</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>3/2014</t>
+        </is>
+      </c>
       <c r="C351" t="inlineStr">
         <is>
           <t>01/12/2016</t>
         </is>
       </c>
       <c r="D351" t="n">
-        <v>13830.54</v>
+        <v>9997.25</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -10693,7 +10697,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Anulação da n.e 756, para atender outras despesas.</t>
+          <t>2º Termo Aditivo ao Termo de Contrato 03/2014 Objeto: Reequilibrio econômico-financeiro de 10,96% mais prorrogação de prazo Valor Global: R$ 119.967,00 Valor Mensal: R$ 9.997,25 Valor Empenhado R$ 9.9</t>
         </is>
       </c>
     </row>
@@ -10730,21 +10734,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2016NE00764</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>3/2014</t>
-        </is>
-      </c>
+          <t>2016NE00759</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr"/>
       <c r="C353" t="inlineStr">
         <is>
           <t>01/12/2016</t>
         </is>
       </c>
       <c r="D353" t="n">
-        <v>9997.25</v>
+        <v>13830.54</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -10753,19 +10753,19 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>2º Termo Aditivo ao Termo de Contrato 03/2014 Objeto: Reequilibrio econômico-financeiro de 10,96% mais prorrogação de prazo Valor Global: R$ 119.967,00 Valor Mensal: R$ 9.997,25 Valor Empenhado R$ 9.9</t>
+          <t>Anulação da n.e 756, para atender outras despesas.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2016NE00767</t>
+          <t>2016NE00765</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>3/2016</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -10774,7 +10774,7 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>454.46</v>
+        <v>1500</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
@@ -10783,14 +10783,14 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Termo de Contrato nº 02/2016 Objeto: Contratação, por dispensa de licitação, compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem para armazenamento de dados. Val</t>
+          <t>Termo de Contrato nº 003/2016-SEAS Objeto: Contratação, por dispensa de licitação, de pessoa jurídica especializada em Licença de uso de Sistema de Informação, para atender as necessidades da Secretar</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2015NE00863</t>
+          <t>2015NE00866</t>
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
@@ -10800,7 +10800,7 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>9009.780000000001</v>
+        <v>8701.379999999999</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2015NE00867</t>
+          <t>2015NE00868</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -10826,7 +10826,7 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>27029.34</v>
+        <v>23904</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2015NE00852</t>
+          <t>2015NE00864</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -10852,7 +10852,7 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>11952</v>
+        <v>8701.379999999999</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2015NE00864</t>
+          <t>2015NE00852</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>8701.379999999999</v>
+        <v>11952</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -10894,7 +10894,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2015NE00868</t>
+          <t>2015NE00867</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>23904</v>
+        <v>27029.34</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2015NE00866</t>
+          <t>2015NE00863</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -10930,7 +10930,7 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>8701.379999999999</v>
+        <v>9009.780000000001</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -10946,17 +10946,21 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2017NE00583</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr"/>
+          <t>2017NE00587</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>10/2016</t>
+        </is>
+      </c>
       <c r="C361" t="inlineStr">
         <is>
           <t>01/11/2017</t>
         </is>
       </c>
       <c r="D361" t="n">
-        <v>3984</v>
+        <v>1450.58</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -10965,14 +10969,14 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Anulação da NE 557 em virtude de Evento incorreto</t>
+          <t>Atender despesa com o Contrato nº 10/2016. Objeto: Serviços de Licença de Uso de Sistema de Informática, Compreendendo a Disponibilização de Gestor de Conteúdo Web, para Publicação de Informações, Not</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2017NE00581</t>
+          <t>2017NE00586</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -10982,7 +10986,7 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>1607.86</v>
+        <v>9954</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -10991,17 +10995,21 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Anulação da NE 558 em virtude de Evento incorreto</t>
+          <t>ANULAÇÃO DA NE EM VIRTUDE DE EVENTO INCORRETO</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2017NE00582</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr"/>
+          <t>2017NE00559</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2/2016</t>
+        </is>
+      </c>
       <c r="C363" t="inlineStr">
         <is>
           <t>01/11/2017</t>
@@ -11017,24 +11025,28 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Anulação da NE 559 em virtude de Evento incorreto</t>
+          <t>Atender o Contrato nº 002/2016-Sistema de Informação compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem website.</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2017NE00590</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr"/>
+          <t>2017NE00560</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>10/2016</t>
+        </is>
+      </c>
       <c r="C364" t="inlineStr">
         <is>
           <t>01/11/2017</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>487.15</v>
+        <v>1450.58</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -11043,19 +11055,19 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Atender o Contrato nº 002/2016-Sistema de Informação compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem website.</t>
+          <t>Atender despesa com o Contrato nº 10/2016. Objeto: Serviços de Licença de Uso de Sistema de Informática, Compreendendo a Disponibilização de Gestor de Conteúdo Web, para Publicação de Informações, Not</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2017NE00603</t>
+          <t>2017NE00557</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>3/2014</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -11064,7 +11076,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>8701.379999999999</v>
+        <v>3984</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -11073,19 +11085,19 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Atender despesa com a RD 0268/2017, do Cont. 03/2014 - Serviços de Acesso a Rede de Governo, referente mês de outubro/14</t>
+          <t>Atender o 1º Termo Aditivo ao Contrato nº 001/2016 Objeto: Serviços de manutenção em equipamentos de informática.</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2017NE00591</t>
+          <t>2017NE00558</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>3/2016</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -11094,7 +11106,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>3984</v>
+        <v>1607.86</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -11103,24 +11115,28 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Atender o 1º Termo Aditivo ao Contrato nº 001/2016 Objeto: Serviços de manutenção em equipamentos de informática.</t>
+          <t>Atender despesa com o Contrato nº 003/2016/SEAS. Objeto: Contratação, por dispensa de licitação, de pessoa jurídica especializada em Licença de uso de Sistema de Informação.</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2017NE00580</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr"/>
+          <t>2017NE00563</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>3/2014</t>
+        </is>
+      </c>
       <c r="C367" t="inlineStr">
         <is>
           <t>01/11/2017</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>1450.58</v>
+        <v>9954</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -11129,24 +11145,28 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Anulação da NE 560 em virtude de Evento incorreto</t>
+          <t>Atender o 3º Temo Aditivo ao Contrato 03/2014-SEAS. Objeto: Realinhamento dos Serviços com base na nova tabela de preços e prorrogação de prazo de vigência (12 meses).</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2017NE00588</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr"/>
+          <t>2017NE00589</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>3/2016</t>
+        </is>
+      </c>
       <c r="C368" t="inlineStr">
         <is>
           <t>01/11/2017</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>9954</v>
+        <v>1607.86</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -11155,7 +11175,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Atender o 3º Temo Aditivo ao Contrato 03/2014-SEAS. Objeto: Realinhamento dos Serviços com base na nova tabela de preços e prorrogação de prazo de vigência (12 meses).</t>
+          <t>Atender despesa com o Contrato nº 003/2016/SEAS. Objeto: Contratação, por dispensa de licitação, de pessoa jurídica especializada em Licença de uso de Sistema de Informação.</t>
         </is>
       </c>
     </row>
@@ -11192,21 +11212,17 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2017NE00589</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>3/2016</t>
-        </is>
-      </c>
+          <t>2017NE00588</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr"/>
       <c r="C370" t="inlineStr">
         <is>
           <t>01/11/2017</t>
         </is>
       </c>
       <c r="D370" t="n">
-        <v>1607.86</v>
+        <v>9954</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -11215,28 +11231,24 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Atender despesa com o Contrato nº 003/2016/SEAS. Objeto: Contratação, por dispensa de licitação, de pessoa jurídica especializada em Licença de uso de Sistema de Informação.</t>
+          <t>Atender o 3º Temo Aditivo ao Contrato 03/2014-SEAS. Objeto: Realinhamento dos Serviços com base na nova tabela de preços e prorrogação de prazo de vigência (12 meses).</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2017NE00563</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>3/2014</t>
-        </is>
-      </c>
+          <t>2017NE00580</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr"/>
       <c r="C371" t="inlineStr">
         <is>
           <t>01/11/2017</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>9954</v>
+        <v>1450.58</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -11245,19 +11257,19 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Atender o 3º Temo Aditivo ao Contrato 03/2014-SEAS. Objeto: Realinhamento dos Serviços com base na nova tabela de preços e prorrogação de prazo de vigência (12 meses).</t>
+          <t>Anulação da NE 560 em virtude de Evento incorreto</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2017NE00558</t>
+          <t>2017NE00591</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>3/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -11266,7 +11278,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>1607.86</v>
+        <v>3984</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -11275,19 +11287,19 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Atender despesa com o Contrato nº 003/2016/SEAS. Objeto: Contratação, por dispensa de licitação, de pessoa jurídica especializada em Licença de uso de Sistema de Informação.</t>
+          <t>Atender o 1º Termo Aditivo ao Contrato nº 001/2016 Objeto: Serviços de manutenção em equipamentos de informática.</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2017NE00557</t>
+          <t>2017NE00603</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>3/2014</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -11296,7 +11308,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>3984</v>
+        <v>8701.379999999999</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -11305,28 +11317,24 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Atender o 1º Termo Aditivo ao Contrato nº 001/2016 Objeto: Serviços de manutenção em equipamentos de informática.</t>
+          <t>Atender despesa com a RD 0268/2017, do Cont. 03/2014 - Serviços de Acesso a Rede de Governo, referente mês de outubro/14</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2017NE00560</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>10/2016</t>
-        </is>
-      </c>
+          <t>2017NE00590</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr"/>
       <c r="C374" t="inlineStr">
         <is>
           <t>01/11/2017</t>
         </is>
       </c>
       <c r="D374" t="n">
-        <v>1450.58</v>
+        <v>487.15</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -11335,21 +11343,17 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Atender despesa com o Contrato nº 10/2016. Objeto: Serviços de Licença de Uso de Sistema de Informática, Compreendendo a Disponibilização de Gestor de Conteúdo Web, para Publicação de Informações, Not</t>
+          <t>Atender o Contrato nº 002/2016-Sistema de Informação compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem website.</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2017NE00559</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>2/2016</t>
-        </is>
-      </c>
+          <t>2017NE00582</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr"/>
       <c r="C375" t="inlineStr">
         <is>
           <t>01/11/2017</t>
@@ -11365,14 +11369,14 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Atender o Contrato nº 002/2016-Sistema de Informação compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem website.</t>
+          <t>Anulação da NE 559 em virtude de Evento incorreto</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2017NE00586</t>
+          <t>2017NE00581</t>
         </is>
       </c>
       <c r="B376" t="inlineStr"/>
@@ -11382,7 +11386,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>9954</v>
+        <v>1607.86</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -11391,28 +11395,24 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>ANULAÇÃO DA NE EM VIRTUDE DE EVENTO INCORRETO</t>
+          <t>Anulação da NE 558 em virtude de Evento incorreto</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2017NE00587</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>10/2016</t>
-        </is>
-      </c>
+          <t>2017NE00583</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr"/>
       <c r="C377" t="inlineStr">
         <is>
           <t>01/11/2017</t>
         </is>
       </c>
       <c r="D377" t="n">
-        <v>1450.58</v>
+        <v>3984</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Atender despesa com o Contrato nº 10/2016. Objeto: Serviços de Licença de Uso de Sistema de Informática, Compreendendo a Disponibilização de Gestor de Conteúdo Web, para Publicação de Informações, Not</t>
+          <t>Anulação da NE 557 em virtude de Evento incorreto</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2019NE00299</t>
+          <t>2019NE00298</t>
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
@@ -11468,7 +11468,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>39776.4</v>
+        <v>5305.35</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -11477,28 +11477,24 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Reforço da NE nº 0219/2019. Termo de Contrato nº 005/2019 - SEAS. Objeto: Contratação de Pessoa Jurídica Especializada no Serviços de Acesso a Internet por Fibra Ótica com com garantia de 100% em down</t>
+          <t>Reforço da NE nº 0167/2019. 3º Termo de Contrato nº 003/2016-SEAS. Objeto:Serviços de Licenciamento de Softwares, Licença de Uso de Sistema de Protocolo em Plataforma Web.</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2019NE00301</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>16/2017</t>
-        </is>
-      </c>
+          <t>2019NE00300</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr"/>
       <c r="C380" t="inlineStr">
         <is>
           <t>01/10/2019</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>109342.2</v>
+        <v>4537.56</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -11507,24 +11503,28 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Reforço da NE nº 0265/2019. 2º Termo Aditivo ao Contrato nº 016/2017 - SEAS. Objeto; Contratação de Empresa Especializada na Prestação dos Serviços de Desenvolvimento e Hospedagem de Sistemas de Infor</t>
+          <t>Reforço da NE nº 222/2019. 3º Termo Aditivo ao Contrato nº 010/2016-SEAS. Objeto: Serviços de Licença e Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para pu</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2019NE00300</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr"/>
+          <t>2019NE00301</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>16/2017</t>
+        </is>
+      </c>
       <c r="C381" t="inlineStr">
         <is>
           <t>01/10/2019</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>4537.56</v>
+        <v>109342.2</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -11533,14 +11533,14 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Reforço da NE nº 222/2019. 3º Termo Aditivo ao Contrato nº 010/2016-SEAS. Objeto: Serviços de Licença e Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para pu</t>
+          <t>Reforço da NE nº 0265/2019. 2º Termo Aditivo ao Contrato nº 016/2017 - SEAS. Objeto; Contratação de Empresa Especializada na Prestação dos Serviços de Desenvolvimento e Hospedagem de Sistemas de Infor</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2019NE00298</t>
+          <t>2019NE00299</t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
@@ -11550,7 +11550,7 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>5305.35</v>
+        <v>39776.4</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Reforço da NE nº 0167/2019. 3º Termo de Contrato nº 003/2016-SEAS. Objeto:Serviços de Licenciamento de Softwares, Licença de Uso de Sistema de Protocolo em Plataforma Web.</t>
+          <t>Reforço da NE nº 0219/2019. Termo de Contrato nº 005/2019 - SEAS. Objeto: Contratação de Pessoa Jurídica Especializada no Serviços de Acesso a Internet por Fibra Ótica com com garantia de 100% em down</t>
         </is>
       </c>
     </row>
@@ -11652,14 +11652,10 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2017NE00401</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>2/2016</t>
-        </is>
-      </c>
+          <t>2017NE00394</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr"/>
       <c r="C386" t="inlineStr">
         <is>
           <t>01/08/2017</t>
@@ -11675,19 +11671,19 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Sistema de informação compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem website.</t>
+          <t>Anulação da NE 390/2017 devido a descrição incorreta</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2017NE00390</t>
+          <t>2017NE00392</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2/2016</t>
+          <t>3/2014</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -11696,7 +11692,7 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>974.3</v>
+        <v>19908</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -11705,28 +11701,24 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Sistema de informação compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem website.</t>
+          <t>SERVIÇOS DE LINK DE COMUNICAÇÃO PARA ATENDER AS NECESSIDADES DA SEAS.</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2017NE00389</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>3/2016</t>
-        </is>
-      </c>
+          <t>2017NE00395</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr"/>
       <c r="C388" t="inlineStr">
         <is>
           <t>01/08/2017</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>3215.72</v>
+        <v>7968</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -11735,14 +11727,14 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LICENCIAMENTO DE SOFTWARES, LICENÇA DE USO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB</t>
+          <t>Anulação Parcial da NE 0217/2017, em virtude de Natureza incorreta</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2017NE00399</t>
+          <t>2017NE00402</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -11765,19 +11757,19 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Anulação Parcial da NE 0218/2017, em virtude de Natureza incorreta</t>
+          <t>SERVIÇOS DE LICENCIAMENTO DE SOFTWARES, LICENÇA DE USO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2017NE00398</t>
+          <t>2017NE00404</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>3/2014</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11786,7 +11778,7 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>19908</v>
+        <v>7968</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -11795,19 +11787,19 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Anulação da NE 0392/2017, em virtude de Natureza incorreta</t>
+          <t>SERVIÇOS DE MANUTENÇÃO EM EQUIPAMENTOS DE INFORMATICA</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2017NE00391</t>
+          <t>2017NE00403</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>3/2014</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -11816,7 +11808,7 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>7968</v>
+        <v>19908</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
@@ -11825,19 +11817,19 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE MANUTENÇÃO EM EQUIPAMENTOS DE INFORMATICA</t>
+          <t>SERVIÇOS DE LINK DE COMUNICAÇÃO PARA ATENDER AS NECESSIDADES DA SEAS.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2017NE00403</t>
+          <t>2017NE00391</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>3/2014</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -11846,7 +11838,7 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>19908</v>
+        <v>7968</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -11855,19 +11847,19 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LINK DE COMUNICAÇÃO PARA ATENDER AS NECESSIDADES DA SEAS.</t>
+          <t>SERVIÇOS DE MANUTENÇÃO EM EQUIPAMENTOS DE INFORMATICA</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2017NE00404</t>
+          <t>2017NE00398</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>3/2014</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -11876,7 +11868,7 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>7968</v>
+        <v>19908</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
@@ -11885,14 +11877,14 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE MANUTENÇÃO EM EQUIPAMENTOS DE INFORMATICA</t>
+          <t>Anulação da NE 0392/2017, em virtude de Natureza incorreta</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2017NE00402</t>
+          <t>2017NE00399</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -11915,24 +11907,28 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LICENCIAMENTO DE SOFTWARES, LICENÇA DE USO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB</t>
+          <t>Anulação Parcial da NE 0218/2017, em virtude de Natureza incorreta</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2017NE00395</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr"/>
+          <t>2017NE00389</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>3/2016</t>
+        </is>
+      </c>
       <c r="C395" t="inlineStr">
         <is>
           <t>01/08/2017</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>7968</v>
+        <v>3215.72</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
@@ -11941,19 +11937,19 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Anulação Parcial da NE 0217/2017, em virtude de Natureza incorreta</t>
+          <t>SERVIÇOS DE LICENCIAMENTO DE SOFTWARES, LICENÇA DE USO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2017NE00392</t>
+          <t>2017NE00390</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>3/2014</t>
+          <t>2/2016</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -11962,7 +11958,7 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>19908</v>
+        <v>974.3</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
@@ -11971,17 +11967,21 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LINK DE COMUNICAÇÃO PARA ATENDER AS NECESSIDADES DA SEAS.</t>
+          <t>Sistema de informação compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem website.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2017NE00394</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr"/>
+          <t>2017NE00401</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>2/2016</t>
+        </is>
+      </c>
       <c r="C397" t="inlineStr">
         <is>
           <t>01/08/2017</t>
@@ -11997,24 +11997,28 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Anulação da NE 390/2017 devido a descrição incorreta</t>
+          <t>Sistema de informação compreendendo o desenvolvimento de Website de transparência a esta Secretaria e hospedagem website.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2016NE00606</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr"/>
+          <t>2016NE00607</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>10/2016</t>
+        </is>
+      </c>
       <c r="C398" t="inlineStr">
         <is>
           <t>01/08/2016</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>8953.559999999999</v>
+        <v>6002.98</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
@@ -12023,19 +12027,19 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Anulação que se faz a n.e 605, por ter sido empenhado a maior</t>
+          <t>Termo de contrato a ser firmado Objeto: Prestação de serviços para licença de uso de sistema de informação, compreendendo a disponibilização de Gestor de conteúdo Web a essa SEAS, para publicações, no</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2016NE00605</t>
+          <t>2016NE00610</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>1/2016</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -12044,7 +12048,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>8953.559999999999</v>
+        <v>7968</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -12053,19 +12057,19 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Termo de contrato a ser firmado Objeto: Prestação de serviços para licença de uso de sistema de informação, compreendendo a disponibilização de Gestor de conteúdo Web a essa SEAS, para publicações, no</t>
+          <t>Contratação de pessoa jurídica especializada em Serviços Técnicos em Informática, para atender as necessidades desta Secretaria e de suas unidades.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2016NE00608</t>
+          <t>2016NE00614</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>3/2014</t>
+          <t>3/2016</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -12074,7 +12078,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>333.24</v>
+        <v>3000</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
@@ -12083,19 +12087,19 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>2º Aditivo ao Termo de Contrato 03/2014 - Diferença de 01 dia do mes de maio</t>
+          <t>Termo de Contrato n. 003/2016- Prestação de Serviço de execução de Sistema de Protocolo em Plataforma Web (SPROWEB), para atender as necessidades da SEAS.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2016NE00614</t>
+          <t>2016NE00608</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>3/2016</t>
+          <t>3/2014</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -12104,7 +12108,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>3000</v>
+        <v>333.24</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -12113,19 +12117,19 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Termo de Contrato n. 003/2016- Prestação de Serviço de execução de Sistema de Protocolo em Plataforma Web (SPROWEB), para atender as necessidades da SEAS.</t>
+          <t>2º Aditivo ao Termo de Contrato 03/2014 - Diferença de 01 dia do mes de maio</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2016NE00610</t>
+          <t>2016NE00605</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>1/2016</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -12134,7 +12138,7 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>7968</v>
+        <v>8953.559999999999</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -12143,28 +12147,24 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>Contratação de pessoa jurídica especializada em Serviços Técnicos em Informática, para atender as necessidades desta Secretaria e de suas unidades.</t>
+          <t>Termo de contrato a ser firmado Objeto: Prestação de serviços para licença de uso de sistema de informação, compreendendo a disponibilização de Gestor de conteúdo Web a essa SEAS, para publicações, no</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2016NE00607</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>10/2016</t>
-        </is>
-      </c>
+          <t>2016NE00606</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr"/>
       <c r="C403" t="inlineStr">
         <is>
           <t>01/08/2016</t>
         </is>
       </c>
       <c r="D403" t="n">
-        <v>6002.98</v>
+        <v>8953.559999999999</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>Termo de contrato a ser firmado Objeto: Prestação de serviços para licença de uso de sistema de informação, compreendendo a disponibilização de Gestor de conteúdo Web a essa SEAS, para publicações, no</t>
+          <t>Anulação que se faz a n.e 605, por ter sido empenhado a maior</t>
         </is>
       </c>
     </row>
@@ -12203,7 +12203,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>Cobertura Financeira do Contrato 003/2016 - 3º Termo Aditivo - SEAS</t>
+          <t>3º Termo de Contrato nº 003/2019-SEAS. Objeto:Serviços de Licenciamento de Softwares, Licença de Uso de Sistema de Protocolo em Plataforma Web.</t>
         </is>
       </c>
     </row>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>Cobertura financeira do 2º Termo Aditivo ao Contrato 010/2016 - Gestor de conteúdo Web.</t>
+          <t>2º Termo Aditivo ao Contrato nº 010/2016-SEAS. Objeto: Serviços de Licença e Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para publicação de informações, no</t>
         </is>
       </c>
     </row>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>2º Termo Aditivo ao Contrato nº 010/2016-SEAS. Objeto: Serviços de Licença e Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para publicação de informações, no</t>
+          <t>Cobertura financeira do 2º Termo Aditivo ao Contrato 010/2016 - Gestor de conteúdo Web.</t>
         </is>
       </c>
     </row>
@@ -12323,19 +12323,19 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>3º Termo de Contrato nº 003/2019-SEAS. Objeto:Serviços de Licenciamento de Softwares, Licença de Uso de Sistema de Protocolo em Plataforma Web.</t>
+          <t>Cobertura Financeira do Contrato 003/2016 - 3º Termo Aditivo - SEAS</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2019NE00085</t>
+          <t>2019NE00082</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>3/2014</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -12344,7 +12344,7 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>4537.56</v>
+        <v>16921.8</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -12353,19 +12353,19 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>2º Termo Aditivo ao Contrato nº 010/2016 - SEAS Objeto: Serviços de Licença e Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para publicação de informações, n</t>
+          <t>4º Termo Aditivo ao Contrato 03/2014 - SEAS Objeto: Serviços de Link de Comunicação para Atender as Necessidades da SEAS.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2019NE00083</t>
+          <t>2019NE00084</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>3/2016</t>
+          <t>16/2017</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -12374,7 +12374,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>5305.35</v>
+        <v>109342.2</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -12383,19 +12383,19 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>3º Termo Aditivo ao Contrato nº 003/2016 - SEAS. Objeto: Serviços de Licenciamento de Softwares, Licença de Uso de Sistema de Protocolo em Plataforma Web.</t>
+          <t>1º TA ao Contrato 016/2017 - Hospedagem de Sistemas</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2019NE00084</t>
+          <t>2019NE00083</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>16/2017</t>
+          <t>3/2016</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -12404,7 +12404,7 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>109342.2</v>
+        <v>5305.35</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
@@ -12413,19 +12413,19 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>1º TA ao Contrato 016/2017 - Hospedagem de Sistemas</t>
+          <t>3º Termo Aditivo ao Contrato nº 003/2016 - SEAS. Objeto: Serviços de Licenciamento de Softwares, Licença de Uso de Sistema de Protocolo em Plataforma Web.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2019NE00082</t>
+          <t>2019NE00085</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>3/2014</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -12434,7 +12434,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>16921.8</v>
+        <v>4537.56</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -12443,19 +12443,19 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>4º Termo Aditivo ao Contrato 03/2014 - SEAS Objeto: Serviços de Link de Comunicação para Atender as Necessidades da SEAS.</t>
+          <t>2º Termo Aditivo ao Contrato nº 010/2016 - SEAS Objeto: Serviços de Licença e Uso de Sistema de Informática compreendendo a disponibilização de gestor de conteúdo web para publicação de informações, n</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2018NE00156</t>
+          <t>2018NE00188</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>3/2014</t>
+          <t>10/2016</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>46783.8</v>
+        <v>18597.58</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -12473,19 +12473,19 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>1º t.a. contrato 03/2014 Prestação de serviços técnicos em telecomunicações com banda larga 3mbps.</t>
+          <t>SERVIÇOS DE LICENCIAMENTO DE SOFTWARES, LICENÇA DE USO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2018NE00188</t>
+          <t>2018NE00156</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>10/2016</t>
+          <t>3/2014</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -12494,7 +12494,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>18597.58</v>
+        <v>46783.8</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
@@ -12503,14 +12503,14 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>SERVIÇOS DE LICENCIAMENTO DE SOFTWARES, LICENÇA DE USO DE SISTEMA DE PROTOCOLO EM PLATAFORMA WEB.</t>
+          <t>1º t.a. contrato 03/2014 Prestação de serviços técnicos em telecomunicações com banda larga 3mbps.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2018NE00068</t>
+          <t>2018NE00067</t>
         </is>
       </c>
       <c r="B415" t="inlineStr"/>
@@ -12520,7 +12520,7 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>10685.99</v>
+        <v>46783.8</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
@@ -12529,14 +12529,14 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>Anulação da NE 051/2018, em virtude de mudança na Natureza de Despesa, conforme orientação da SEFAZ.</t>
+          <t>Anulação da NE 064/2018, em virtude de mudança na Natureza de Despesa, conforme orientação da SEFAZ.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2018NE00067</t>
+          <t>2018NE00068</t>
         </is>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -12546,7 +12546,7 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>46783.8</v>
+        <v>10685.99</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>Anulação da NE 064/2018, em virtude de mudança na Natureza de Despesa, conforme orientação da SEFAZ.</t>
+          <t>Anulação da NE 051/2018, em virtude de mudança na Natureza de Despesa, conforme orientação da SEFAZ.</t>
         </is>
       </c>
     </row>
